--- a/outputs/NTPC_model.xlsx
+++ b/outputs/NTPC_model.xlsx
@@ -4,49 +4,68 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" firstSheet="4" activeTab="3"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" firstSheet="5" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
     <sheet name="Inputs" sheetId="2" r:id="rId2"/>
     <sheet name="Model" sheetId="3" r:id="rId3"/>
     <sheet name="DCF" sheetId="4" r:id="rId4"/>
-    <sheet name="Comps" sheetId="5" r:id="rId5"/>
-    <sheet name="Guidance" sheetId="6" r:id="rId6"/>
+    <sheet name="SOTP" sheetId="5" r:id="rId5"/>
+    <sheet name="Comps" sheetId="6" r:id="rId6"/>
+    <sheet name="Guidance" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="in_beta_raw">Inputs!$C$10</definedName>
-    <definedName name="in_capz">Inputs!$C$24</definedName>
-    <definedName name="in_cash">Inputs!$C$16</definedName>
-    <definedName name="in_debt_share">Inputs!$C$25</definedName>
-    <definedName name="in_dep">Inputs!$C$23</definedName>
-    <definedName name="in_drift">Inputs!$C$21</definedName>
+    <definedName name="in_beta_raw">Inputs!$C$11</definedName>
+    <definedName name="in_capz">Inputs!$C$32</definedName>
+    <definedName name="in_cash">Inputs!$C$17</definedName>
+    <definedName name="in_debt_share">Inputs!$C$33</definedName>
+    <definedName name="in_dep">Inputs!$C$31</definedName>
     <definedName name="in_ds">Inputs!$C$5</definedName>
     <definedName name="in_erp">Inputs!$C$6</definedName>
-    <definedName name="in_execution">Inputs!$C$19</definedName>
-    <definedName name="in_g">Inputs!$C$12</definedName>
+    <definedName name="in_execution">Inputs!$C$20</definedName>
+    <definedName name="in_g">Inputs!$C$13</definedName>
     <definedName name="in_gsec">Inputs!$C$4</definedName>
-    <definedName name="in_int">Inputs!$C$26</definedName>
-    <definedName name="in_inv_g">Inputs!$C$30</definedName>
-    <definedName name="in_kd">Inputs!$C$11</definedName>
-    <definedName name="in_mi">Inputs!$C$17</definedName>
-    <definedName name="in_mult">Inputs!$C$18</definedName>
-    <definedName name="in_oa">Inputs!$C$28</definedName>
-    <definedName name="in_oi">Inputs!$C$22</definedName>
-    <definedName name="in_ol">Inputs!$C$29</definedName>
-    <definedName name="in_payout">Inputs!$C$27</definedName>
-    <definedName name="in_price">Inputs!$C$14</definedName>
-    <definedName name="in_ronic">Inputs!$C$13</definedName>
-    <definedName name="in_shares">Inputs!$C$15</definedName>
+    <definedName name="in_holdco">Inputs!$C$46</definedName>
+    <definedName name="in_int">Inputs!$C$34</definedName>
+    <definedName name="in_inv_g">Inputs!$C$38</definedName>
+    <definedName name="in_jv0">Inputs!$C$28</definedName>
+    <definedName name="in_jv_g">Inputs!$C$29</definedName>
+    <definedName name="in_kd">Inputs!$C$12</definedName>
+    <definedName name="in_mi">Inputs!$C$18</definedName>
+    <definedName name="in_min_cash">Inputs!$C$10</definedName>
+    <definedName name="in_mult">Inputs!$C$19</definedName>
+    <definedName name="in_ngel_mcap">Inputs!$C$44</definedName>
+    <definedName name="in_ngel_stake">Inputs!$C$45</definedName>
+    <definedName name="in_oa">Inputs!$C$36</definedName>
+    <definedName name="in_oi">Inputs!$C$30</definedName>
+    <definedName name="in_ol">Inputs!$C$37</definedName>
+    <definedName name="in_payout">Inputs!$C$35</definedName>
+    <definedName name="in_pb_g">Inputs!$C$43</definedName>
+    <definedName name="in_price">Inputs!$C$15</definedName>
+    <definedName name="in_re_cost">Inputs!$C$22</definedName>
+    <definedName name="in_re_cuf">Inputs!$C$23</definedName>
+    <definedName name="in_re_margin">Inputs!$C$25</definedName>
+    <definedName name="in_re_mw0">Inputs!$C$27</definedName>
+    <definedName name="in_re_mw_prev">Inputs!$C$26</definedName>
+    <definedName name="in_re_share">Inputs!$C$21</definedName>
+    <definedName name="in_re_tariff">Inputs!$C$24</definedName>
+    <definedName name="in_regeq0">Inputs!$C$40</definedName>
+    <definedName name="in_regeq_prev">Inputs!$C$39</definedName>
+    <definedName name="in_regshare">Inputs!$C$41</definedName>
+    <definedName name="in_roe">Inputs!$C$42</definedName>
+    <definedName name="in_ronic">Inputs!$C$14</definedName>
+    <definedName name="in_shares">Inputs!$C$16</definedName>
     <definedName name="in_stub">Inputs!$C$8</definedName>
     <definedName name="in_tax">Inputs!$C$7</definedName>
     <definedName name="in_w_dcf">Inputs!$C$9</definedName>
-    <definedName name="in_yield">Inputs!$C$20</definedName>
+    <definedName name="out_dcf_12m">DCF!$C$36</definedName>
     <definedName name="out_dcf_ps">DCF!$C$34</definedName>
-    <definedName name="out_rating">DCF!$C$40</definedName>
-    <definedName name="out_rel_ps">DCF!$C$37</definedName>
-    <definedName name="out_tp">DCF!$C$38</definedName>
-    <definedName name="out_upside">DCF!$C$39</definedName>
+    <definedName name="out_rating">DCF!$C$42</definedName>
+    <definedName name="out_rel_ps">DCF!$C$38</definedName>
+    <definedName name="out_sotp_ps">DCF!$C$39</definedName>
+    <definedName name="out_tp">DCF!$C$40</definedName>
+    <definedName name="out_upside">DCF!$C$41</definedName>
     <definedName name="wacc">DCF!$C$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -54,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="531">
   <si>
     <t>NTPC Ltd - inputs (Rs crore)</t>
   </si>
@@ -98,10 +117,16 @@
     <t>Valuation date 25-Sep-2026</t>
   </si>
   <si>
-    <t>Weight on DCF in target</t>
-  </si>
-  <si>
-    <t>Balance on peer EV/EBITDA</t>
+    <t>Weight on 12m DCF in target (non-regulated)</t>
+  </si>
+  <si>
+    <t>Balance on FY27E EV/EBITDA</t>
+  </si>
+  <si>
+    <t>Incremental cash floor</t>
+  </si>
+  <si>
+    <t>Shortfalls drawn on a revolver</t>
   </si>
   <si>
     <t>Raw beta (2y weekly vs Nifty 50)</t>
@@ -125,9 +150,6 @@
     <t>Return on new invested capital (terminal)</t>
   </si>
   <si>
-    <t>Regulated return on equity 15.5% (CMD, Q1FY27); RONIC set at 12% on total capital.</t>
-  </si>
-  <si>
     <t>Share price (Rs)</t>
   </si>
   <si>
@@ -158,16 +180,43 @@
     <t>Capex execution vs guidance</t>
   </si>
   <si>
-    <t>Q1FY27 call: group capex Rs 1,08,000 cr for FY27; Rs 5,97,000 cr over FY28-32 (Rs 1,19,400 cr/yr). FY26 actual was Rs 49,068 cr, so a 2.2x step-up is assumed to be delivered at 70%.</t>
-  </si>
-  <si>
-    <t>EBITDA yield on commissioned assets</t>
-  </si>
-  <si>
-    <t>EBITDA grows with commissioned assets: ~90 GW commercial today, 150 GW targeted by FY32. Revenue is backed out from EBITDA and the margin path.</t>
-  </si>
-  <si>
-    <t>EBITDA growth of existing assets</t>
+    <t>Q1FY27 call: group capex Rs 1,08,000 cr for FY27, Rs 5,97,000 cr over FY28-32 (Rs 1,19,400 cr/yr) and Rs 9,63,000 cr over FY33-37, mostly nuclear. FY26 actual was Rs 49,068 cr, so the step-up is haircut to 70%. FY33-36 is held at the FY28-32 run-rate because long-gestation nuclear capex adds little EBITDA in the horizon.</t>
+  </si>
+  <si>
+    <t>RE share of assets commissioned</t>
+  </si>
+  <si>
+    <t>Group RE 11,578 MW at Mar-26 (12,068 MW incl. 490 MW added in FY27, Q4FY26 call); NGEL generated 14.6 BU in FY26 (implied CUF ~18.5%) on TTM revenue of Rs 3,285 cr (~Rs 2.25/kWh). NGEL capex Rs 35,800 cr for ~8 GW (Rs 4.5 cr/MW); about half of group capex goes to RE (Q4FY26 call). At guided capex the model commissions ~7 GW of RE in FY27 vs 7-8 GW guided.</t>
+  </si>
+  <si>
+    <t>RE cost (Rs cr per MW)</t>
+  </si>
+  <si>
+    <t>RE capacity utilisation (CUF)</t>
+  </si>
+  <si>
+    <t>RE tariff (Rs/kWh)</t>
+  </si>
+  <si>
+    <t>RE EBITDA margin</t>
+  </si>
+  <si>
+    <t>RE MW at FY25 (for FY26 calibration)</t>
+  </si>
+  <si>
+    <t>RE MW at FY26</t>
+  </si>
+  <si>
+    <t>NTPC: reported; others: FY26 RE commissioning / cost per MW</t>
+  </si>
+  <si>
+    <t>Share of JV profit FY26</t>
+  </si>
+  <si>
+    <t>Q4FY26 call</t>
+  </si>
+  <si>
+    <t>JV profit growth</t>
   </si>
   <si>
     <t>Other income % of sales</t>
@@ -179,10 +228,10 @@
     <t>Capitalisation % of (CWIP + capex)</t>
   </si>
   <si>
-    <t>New debt % of capex</t>
-  </si>
-  <si>
-    <t>Interest % average debt</t>
+    <t>New term debt % of capex</t>
+  </si>
+  <si>
+    <t>Interest % average debt (and revolver)</t>
   </si>
   <si>
     <t>Dividend payout</t>
@@ -194,10 +243,49 @@
     <t>Other (non-cash) assets % of sales</t>
   </si>
   <si>
-    <t>Other liabilities % of sales</t>
-  </si>
-  <si>
-    <t>Investments growth</t>
+    <t>Other liabilities (ex minorities) % of sales</t>
+  </si>
+  <si>
+    <t>Investments growth (cash)</t>
+  </si>
+  <si>
+    <t>Regulated equity FY25</t>
+  </si>
+  <si>
+    <t>Consolidated regulated equity Rs 1,20,319 cr at Mar-26 vs Rs 1,08,791 cr a year earlier (Q4FY26 call); regulated RoE 15.5% post-tax (CMD, Q1FY27).</t>
+  </si>
+  <si>
+    <t>Regulated equity FY26</t>
+  </si>
+  <si>
+    <t>Normative equity share of regulated capital</t>
+  </si>
+  <si>
+    <t>CERC</t>
+  </si>
+  <si>
+    <t>Earned RoE on regulated equity</t>
+  </si>
+  <si>
+    <t>15.5% normative + net operational gains</t>
+  </si>
+  <si>
+    <t>Regulated equity growth after FY36</t>
+  </si>
+  <si>
+    <t>NTPC Green market cap</t>
+  </si>
+  <si>
+    <t>NSE 2026-09-25</t>
+  </si>
+  <si>
+    <t>NTPC stake in NTPC Green</t>
+  </si>
+  <si>
+    <t>Jun-2026 shareholding</t>
+  </si>
+  <si>
+    <t>Holding-company discount</t>
   </si>
   <si>
     <t>NTPC Ltd - consolidated model (Rs crore)</t>
@@ -239,7 +327,19 @@
     <t>FY33E</t>
   </si>
   <si>
-    <t>Drivers</t>
+    <t>FY34E</t>
+  </si>
+  <si>
+    <t>FY35E</t>
+  </si>
+  <si>
+    <t>FY36E</t>
+  </si>
+  <si>
+    <t>Capex and commissioning</t>
+  </si>
+  <si>
+    <t>EBITDA build</t>
   </si>
   <si>
     <t>Income statement</t>
@@ -248,9 +348,6 @@
     <t>Balance sheet</t>
   </si>
   <si>
-    <t>Capex and commissioning</t>
-  </si>
-  <si>
     <t>Cash flow</t>
   </si>
   <si>
@@ -260,22 +357,49 @@
     <t>Capex guided (mgmt)</t>
   </si>
   <si>
+    <t>Capex</t>
+  </si>
+  <si>
+    <t>Assets commissioned (CWIP to block)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  of which renewables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  of which core / regulated</t>
+  </si>
+  <si>
+    <t>Renewable capacity (MW)</t>
+  </si>
+  <si>
+    <t>Renewable revenue</t>
+  </si>
+  <si>
+    <t>Renewable EBITDA</t>
+  </si>
+  <si>
+    <t>Regulated equity</t>
+  </si>
+  <si>
+    <t>Regulated (core) EBITDA</t>
+  </si>
+  <si>
+    <t>EBITDA</t>
+  </si>
+  <si>
     <t>EBITDA margin</t>
   </si>
   <si>
     <t>Revenue</t>
   </si>
   <si>
-    <t>EBITDA</t>
-  </si>
-  <si>
     <t>Other income</t>
   </si>
   <si>
     <t>Depreciation</t>
   </si>
   <si>
-    <t>Interest</t>
+    <t>Interest (term debt + opening revolver)</t>
   </si>
   <si>
     <t>Profit before tax</t>
@@ -284,9 +408,18 @@
     <t>Tax</t>
   </si>
   <si>
+    <t>Share of JV profit</t>
+  </si>
+  <si>
     <t>Net profit</t>
   </si>
   <si>
+    <t>Minority share of profit</t>
+  </si>
+  <si>
+    <t>Net profit to shareholders</t>
+  </si>
+  <si>
     <t>EPS (Rs)</t>
   </si>
   <si>
@@ -305,7 +438,7 @@
     <t>Other assets (non-cash)</t>
   </si>
   <si>
-    <t>Cash build from FY26</t>
+    <t>Incremental cash (floor, see revolver)</t>
   </si>
   <si>
     <t>Total assets</t>
@@ -317,10 +450,16 @@
     <t>Reserves</t>
   </si>
   <si>
-    <t>Borrowings</t>
-  </si>
-  <si>
-    <t>Other liabilities</t>
+    <t>Minority interest</t>
+  </si>
+  <si>
+    <t>Borrowings (term)</t>
+  </si>
+  <si>
+    <t>Revolver</t>
+  </si>
+  <si>
+    <t>Other liabilities (ex minorities from FY26)</t>
   </si>
   <si>
     <t>Total liabilities &amp; equity</t>
@@ -329,12 +468,6 @@
     <t>Balance check (assets - liabilities)</t>
   </si>
   <si>
-    <t>Capex</t>
-  </si>
-  <si>
-    <t>Assets commissioned (CWIP to block)</t>
-  </si>
-  <si>
     <t>Increase in net working capital</t>
   </si>
   <si>
@@ -344,6 +477,15 @@
     <t>Cash from investing</t>
   </si>
   <si>
+    <t>Term debt raised less dividends</t>
+  </si>
+  <si>
+    <t>Cash before revolver</t>
+  </si>
+  <si>
+    <t>Revolver draw / (repayment)</t>
+  </si>
+  <si>
     <t>Cash from financing</t>
   </si>
   <si>
@@ -431,31 +573,85 @@
     <t>Less: minority interest</t>
   </si>
   <si>
+    <t>Equity value today</t>
+  </si>
+  <si>
+    <t>DCF value per share today (Rs)</t>
+  </si>
+  <si>
+    <t>Terminal value share of EV</t>
+  </si>
+  <si>
+    <t>DCF value in 12 months (grown at Ke, less FY27 DPS)</t>
+  </si>
+  <si>
+    <t>Peer EV/EBITDA x FY27E EBITDA</t>
+  </si>
+  <si>
+    <t>EV/EBITDA value in 12 months (Rs)</t>
+  </si>
+  <si>
+    <t>SOTP value per share (Rs, regulated only)</t>
+  </si>
+  <si>
+    <t>12-month target price (Rs)</t>
+  </si>
+  <si>
+    <t>Upside / (downside)</t>
+  </si>
+  <si>
+    <t>Rating</t>
+  </si>
+  <si>
+    <t>DCF value per share today: WACC (rows) x terminal growth (cols)</t>
+  </si>
+  <si>
+    <t>NTPC Ltd - sum of the parts at Mar-27</t>
+  </si>
+  <si>
+    <t>Residual income on regulated equity</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>Regulated equity (closing)</t>
+  </si>
+  <si>
+    <t>Residual income (RoE - Ke) x opening</t>
+  </si>
+  <si>
+    <t>PV</t>
+  </si>
+  <si>
+    <t>Regulated equity FY27E (book)</t>
+  </si>
+  <si>
+    <t>PV of residual income FY28-FY36</t>
+  </si>
+  <si>
+    <t>PV of terminal residual income</t>
+  </si>
+  <si>
+    <t>Regulated equity value</t>
+  </si>
+  <si>
+    <t>Implied P/B on FY27E regulated equity</t>
+  </si>
+  <si>
+    <t>Equity in regulated CWIP at book</t>
+  </si>
+  <si>
+    <t>NTPC Green stake at market less holdco discount</t>
+  </si>
+  <si>
     <t>Equity value</t>
   </si>
   <si>
-    <t>DCF value per share (Rs)</t>
-  </si>
-  <si>
-    <t>Terminal value share of EV</t>
-  </si>
-  <si>
-    <t>Peer EV/EBITDA x FY26A EBITDA</t>
-  </si>
-  <si>
-    <t>Relative value per share (Rs)</t>
-  </si>
-  <si>
-    <t>Target price (Rs)</t>
-  </si>
-  <si>
-    <t>Upside / (downside)</t>
-  </si>
-  <si>
-    <t>Rating</t>
-  </si>
-  <si>
-    <t>DCF value per share: WACC (rows) x terminal growth (cols)</t>
+    <t>SOTP value per share (Rs)</t>
+  </si>
+  <si>
+    <t>JVs are not added: consolidated regulated equity already includes them.</t>
   </si>
   <si>
     <t>NTPC Ltd</t>
@@ -467,13 +663,22 @@
     <t>Upside</t>
   </si>
   <si>
-    <t>DCF value (Rs)</t>
-  </si>
-  <si>
-    <t>Peer-multiple value (Rs)</t>
-  </si>
-  <si>
-    <t>Blue = input, black = formula. Change Inputs or the capex/margin rows on Model.</t>
+    <t>SOTP value (Rs)</t>
+  </si>
+  <si>
+    <t>DCF value today (Rs)</t>
+  </si>
+  <si>
+    <t>DCF value in 12m (Rs)</t>
+  </si>
+  <si>
+    <t>FY27E EV/EBITDA value (Rs)</t>
+  </si>
+  <si>
+    <t>Method: sum of the parts; DCF and EV/EBITDA are cross-checks.</t>
+  </si>
+  <si>
+    <t>Blue = input, black = formula. Change Inputs or the guided-capex row on Model.</t>
   </si>
   <si>
     <t>Prices as of 2026-09-25. Student research exercise, not investment advice.</t>
@@ -1889,89 +2094,112 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="1" max="1" width="34.7109375" customWidth="1"/>
     <col min="2" max="2" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>134</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>132</v>
+        <v>175</v>
       </c>
       <c r="B3" s="3">
-        <f>DCF!$C$40</f>
+        <f>DCF!$C$42</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>130</v>
+        <v>173</v>
       </c>
       <c r="B4" s="4">
-        <f>DCF!$C$38</f>
+        <f>DCF!$C$40</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>135</v>
+        <v>194</v>
       </c>
       <c r="B5" s="5">
-        <f>Inputs!$C$14</f>
+        <f>Inputs!$C$15</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="B6" s="6">
-        <f>DCF!$C$39</f>
+        <f>DCF!$C$41</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="B7" s="5">
-        <f>DCF!$C$34</f>
+        <f>DCF!$C$39</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="B8" s="5">
-        <f>DCF!$C$37</f>
+        <f>DCF!$C$34</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B9" s="6">
+        <v>198</v>
+      </c>
+      <c r="B9" s="5">
+        <f>DCF!$C$36</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B10" s="5">
+        <f>DCF!$C$38</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B11" s="6">
         <f>DCF!$C$11</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="7" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="7" t="s">
-        <v>140</v>
+    <row r="13" spans="1:2">
+      <c r="A13" s="7" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="7" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="7" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -1981,13 +2209,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.7109375" customWidth="1"/>
     <col min="2" max="2" width="8.7109375" customWidth="1"/>
     <col min="3" max="3" width="14.7109375" customWidth="1"/>
-    <col min="4" max="4" width="70.7109375" customWidth="1"/>
+    <col min="4" max="4" width="90.7109375" customWidth="1"/>
     <col min="5" max="17" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2078,8 +2306,8 @@
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="9">
-        <v>0.797</v>
+      <c r="C10" s="10">
+        <v>0</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>17</v>
@@ -2089,8 +2317,8 @@
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="8">
-        <v>0.074</v>
+      <c r="C11" s="9">
+        <v>0.797</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>19</v>
@@ -2101,7 +2329,7 @@
         <v>20</v>
       </c>
       <c r="C12" s="8">
-        <v>0.05</v>
+        <v>0.074</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>21</v>
@@ -2112,7 +2340,7 @@
         <v>22</v>
       </c>
       <c r="C13" s="8">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>23</v>
@@ -2122,94 +2350,94 @@
       <c r="A14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="10">
-        <v>326.6</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>25</v>
-      </c>
+      <c r="C14" s="8">
+        <v>0.12</v>
+      </c>
+      <c r="D14" s="7"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="10">
+        <v>326.6</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>26</v>
-      </c>
-      <c r="C15" s="9">
-        <v>969.6666134</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="9">
+        <v>969.6666134</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="C16" s="10">
-        <v>6449.68</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="10">
+        <v>6449.68</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>30</v>
-      </c>
-      <c r="C17" s="10">
-        <v>7977.39</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="11">
-        <v>14.15362587744053</v>
+      <c r="C18" s="10">
+        <v>7977.39</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="11">
+        <v>14.15362587744053</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>33</v>
-      </c>
-      <c r="C19" s="8">
-        <v>0.7</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>35</v>
-      </c>
-      <c r="C20" s="8">
-        <v>0.14</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C21" s="8">
-        <v>0</v>
-      </c>
-      <c r="D21" s="7"/>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="8">
-        <v>0.025</v>
+      <c r="C22" s="9">
+        <v>4.5</v>
       </c>
       <c r="D22" s="7"/>
     </row>
@@ -2218,7 +2446,7 @@
         <v>39</v>
       </c>
       <c r="C23" s="8">
-        <v>0.07000000000000001</v>
+        <v>0.185</v>
       </c>
       <c r="D23" s="7"/>
     </row>
@@ -2226,8 +2454,8 @@
       <c r="A24" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="8">
-        <v>0.4</v>
+      <c r="C24" s="9">
+        <v>2.3</v>
       </c>
       <c r="D24" s="7"/>
     </row>
@@ -2236,7 +2464,7 @@
         <v>41</v>
       </c>
       <c r="C25" s="8">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="D25" s="7"/>
     </row>
@@ -2244,8 +2472,8 @@
       <c r="A26" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="8">
-        <v>0.055</v>
+      <c r="C26" s="10">
+        <v>6840</v>
       </c>
       <c r="D26" s="7"/>
     </row>
@@ -2253,8 +2481,8 @@
       <c r="A27" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C27" s="8">
-        <v>0.32</v>
+      <c r="C27" s="10">
+        <v>11578</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>44</v>
@@ -2264,28 +2492,186 @@
       <c r="A28" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="8">
-        <v>0.7</v>
-      </c>
-      <c r="D28" s="7"/>
+      <c r="C28" s="10">
+        <v>2864</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C29" s="8">
-        <v>0.45</v>
+        <v>0.05</v>
       </c>
       <c r="D29" s="7"/>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C30" s="8">
+        <v>0.025</v>
+      </c>
+      <c r="D30" s="7"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" s="8">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D31" s="7"/>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="D32" s="7"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D33" s="7"/>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" s="8">
+        <v>0.055</v>
+      </c>
+      <c r="D34" s="7"/>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" s="8">
+        <v>0.32</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="D36" s="7"/>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" s="8">
+        <v>0.41</v>
+      </c>
+      <c r="D37" s="7"/>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38" s="8">
         <v>0.05</v>
       </c>
-      <c r="D30" s="7"/>
+      <c r="D38" s="7"/>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C39" s="10">
+        <v>108791</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C40" s="10">
+        <v>120319</v>
+      </c>
+      <c r="D40" s="7"/>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C41" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C42" s="8">
+        <v>0.159</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C43" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="D43" s="7"/>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C44" s="10">
+        <v>78760.90444474769</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C45" s="8">
+        <v>0.8901</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C46" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="D46" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2294,7 +2680,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:Q56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.7109375" customWidth="1"/>
@@ -2302,54 +2688,63 @@
     <col min="3" max="17" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>83</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="12" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
@@ -2364,10 +2759,13 @@
       <c r="L4" s="12"/>
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" s="12"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="12"/>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="2" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="H5" s="10">
         <v>108000</v>
@@ -2388,546 +2786,630 @@
         <v>119400</v>
       </c>
       <c r="N5" s="10">
-        <v>110000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>119400</v>
+      </c>
+      <c r="O5" s="10">
+        <v>119400</v>
+      </c>
+      <c r="P5" s="10">
+        <v>119400</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>119400</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" s="6">
-        <f>C9/C8</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="6">
-        <f>D9/D8</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="6">
-        <f>E9/E8</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="6">
-        <f>F9/F8</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="6">
-        <f>G9/G8</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="8">
-        <v>0.3</v>
-      </c>
-      <c r="I6" s="8">
-        <v>0.305</v>
-      </c>
-      <c r="J6" s="8">
-        <v>0.31</v>
-      </c>
-      <c r="K6" s="8">
-        <v>0.315</v>
-      </c>
-      <c r="L6" s="8">
-        <v>0.32</v>
-      </c>
-      <c r="M6" s="8">
-        <v>0.325</v>
-      </c>
-      <c r="N6" s="8">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="12"/>
-    </row>
-    <row r="8" spans="1:14">
+        <v>94</v>
+      </c>
+      <c r="C6" s="5">
+        <v>29086</v>
+      </c>
+      <c r="D6" s="5">
+        <v>28346</v>
+      </c>
+      <c r="E6" s="5">
+        <v>33199</v>
+      </c>
+      <c r="F6" s="5">
+        <v>43099</v>
+      </c>
+      <c r="G6" s="5">
+        <v>50987</v>
+      </c>
+      <c r="H6" s="5">
+        <f>H5*Inputs!$C$20</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <f>I5*Inputs!$C$20</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <f>J5*Inputs!$C$20</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <f>K5*Inputs!$C$20</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <f>L5*Inputs!$C$20</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <f>M5*Inputs!$C$20</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <f>N5*Inputs!$C$20</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="5">
+        <f>O5*Inputs!$C$20</f>
+        <v>0</v>
+      </c>
+      <c r="P6" s="5">
+        <f>P5*Inputs!$C$20</f>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="5">
+        <f>Q5*Inputs!$C$20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="5">
+        <v>35466</v>
+      </c>
+      <c r="D7" s="5">
+        <v>30293</v>
+      </c>
+      <c r="E7" s="5">
+        <v>34714</v>
+      </c>
+      <c r="F7" s="5">
+        <v>29904</v>
+      </c>
+      <c r="G7" s="5">
+        <v>66889</v>
+      </c>
+      <c r="H7" s="5">
+        <f>(G33+H6)*Inputs!$C$32</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <f>(H33+I6)*Inputs!$C$32</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <f>(I33+J6)*Inputs!$C$32</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <f>(J33+K6)*Inputs!$C$32</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <f>(K33+L6)*Inputs!$C$32</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <f>(L33+M6)*Inputs!$C$32</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <f>(M33+N6)*Inputs!$C$32</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="5">
+        <f>(N33+O6)*Inputs!$C$32</f>
+        <v>0</v>
+      </c>
+      <c r="P7" s="5">
+        <f>(O33+P6)*Inputs!$C$32</f>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="5">
+        <f>(P33+Q6)*Inputs!$C$32</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="5">
-        <v>132669</v>
-      </c>
-      <c r="D8" s="5">
-        <v>176207</v>
-      </c>
-      <c r="E8" s="5">
-        <v>178525</v>
-      </c>
-      <c r="F8" s="5">
-        <v>188138</v>
+        <v>96</v>
       </c>
       <c r="G8" s="5">
-        <v>187385</v>
+        <f>G7*Inputs!$C$21</f>
+        <v>0</v>
       </c>
       <c r="H8" s="5">
-        <f>H9/H6</f>
+        <f>H7*Inputs!$C$21</f>
         <v>0</v>
       </c>
       <c r="I8" s="5">
-        <f>I9/I6</f>
+        <f>I7*Inputs!$C$21</f>
         <v>0</v>
       </c>
       <c r="J8" s="5">
-        <f>J9/J6</f>
+        <f>J7*Inputs!$C$21</f>
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <f>K9/K6</f>
+        <f>K7*Inputs!$C$21</f>
         <v>0</v>
       </c>
       <c r="L8" s="5">
-        <f>L9/L6</f>
+        <f>L7*Inputs!$C$21</f>
         <v>0</v>
       </c>
       <c r="M8" s="5">
-        <f>M9/M6</f>
+        <f>M7*Inputs!$C$21</f>
         <v>0</v>
       </c>
       <c r="N8" s="5">
-        <f>N9/N6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <f>N7*Inputs!$C$21</f>
+        <v>0</v>
+      </c>
+      <c r="O8" s="5">
+        <f>O7*Inputs!$C$21</f>
+        <v>0</v>
+      </c>
+      <c r="P8" s="5">
+        <f>P7*Inputs!$C$21</f>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="5">
+        <f>Q7*Inputs!$C$21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="5">
+        <v>97</v>
+      </c>
+      <c r="G9" s="5">
+        <f>G7-G8</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <f>H7-H8</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <f>I7-I8</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <f>J7-J8</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <f>K7-K8</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <f>L7-L8</f>
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <f>M7-M8</f>
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <f>N7-N8</f>
+        <v>0</v>
+      </c>
+      <c r="O9" s="5">
+        <f>O7-O8</f>
+        <v>0</v>
+      </c>
+      <c r="P9" s="5">
+        <f>P7-P8</f>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="5">
+        <f>Q7-Q8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12"/>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G11" s="5">
+        <f>Inputs!$C$27</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <f>G11+H8/Inputs!$C$22</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <f>H11+I8/Inputs!$C$22</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <f>I11+J8/Inputs!$C$22</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <f>J11+K8/Inputs!$C$22</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <f>K11+L8/Inputs!$C$22</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <f>L11+M8/Inputs!$C$22</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <f>M11+N8/Inputs!$C$22</f>
+        <v>0</v>
+      </c>
+      <c r="O11" s="5">
+        <f>N11+O8/Inputs!$C$22</f>
+        <v>0</v>
+      </c>
+      <c r="P11" s="5">
+        <f>O11+P8/Inputs!$C$22</f>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="5">
+        <f>P11+Q8/Inputs!$C$22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G12" s="5">
+        <f>(Inputs!$C$26+Inputs!$C$27)/2*Inputs!$C$23*0.876*Inputs!$C$24</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <f>(G11+H11)/2*Inputs!$C$23*0.876*Inputs!$C$24</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <f>(H11+I11)/2*Inputs!$C$23*0.876*Inputs!$C$24</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <f>(I11+J11)/2*Inputs!$C$23*0.876*Inputs!$C$24</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <f>(J11+K11)/2*Inputs!$C$23*0.876*Inputs!$C$24</f>
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <f>(K11+L11)/2*Inputs!$C$23*0.876*Inputs!$C$24</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <f>(L11+M11)/2*Inputs!$C$23*0.876*Inputs!$C$24</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <f>(M11+N11)/2*Inputs!$C$23*0.876*Inputs!$C$24</f>
+        <v>0</v>
+      </c>
+      <c r="O12" s="5">
+        <f>(N11+O11)/2*Inputs!$C$23*0.876*Inputs!$C$24</f>
+        <v>0</v>
+      </c>
+      <c r="P12" s="5">
+        <f>(O11+P11)/2*Inputs!$C$23*0.876*Inputs!$C$24</f>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="5">
+        <f>(P11+Q11)/2*Inputs!$C$23*0.876*Inputs!$C$24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G13" s="5">
+        <f>G12*Inputs!$C$25</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <f>H12*Inputs!$C$25</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <f>I12*Inputs!$C$25</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <f>J12*Inputs!$C$25</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <f>K12*Inputs!$C$25</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <f>L12*Inputs!$C$25</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <f>M12*Inputs!$C$25</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <f>N12*Inputs!$C$25</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="5">
+        <f>O12*Inputs!$C$25</f>
+        <v>0</v>
+      </c>
+      <c r="P13" s="5">
+        <f>P12*Inputs!$C$25</f>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="5">
+        <f>Q12*Inputs!$C$25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G14" s="5">
+        <f>Inputs!$C$40</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <f>G14+Inputs!$C$41*H9</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <f>H14+Inputs!$C$41*I9</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <f>I14+Inputs!$C$41*J9</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <f>J14+Inputs!$C$41*K9</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <f>K14+Inputs!$C$41*L9</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <f>L14+Inputs!$C$41*M9</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <f>M14+Inputs!$C$41*N9</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="5">
+        <f>N14+Inputs!$C$41*O9</f>
+        <v>0</v>
+      </c>
+      <c r="P14" s="5">
+        <f>O14+Inputs!$C$41*P9</f>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="5">
+        <f>P14+Inputs!$C$41*Q9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G15" s="5">
+        <f>G16-G13</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <f>$G$15*(G14+H14)/2/((Inputs!$C$39+Inputs!$C$40)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <f>$G$15*(H14+I14)/2/((Inputs!$C$39+Inputs!$C$40)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <f>$G$15*(I14+J14)/2/((Inputs!$C$39+Inputs!$C$40)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <f>$G$15*(J14+K14)/2/((Inputs!$C$39+Inputs!$C$40)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <f>$G$15*(K14+L14)/2/((Inputs!$C$39+Inputs!$C$40)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <f>$G$15*(L14+M14)/2/((Inputs!$C$39+Inputs!$C$40)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <f>$G$15*(M14+N14)/2/((Inputs!$C$39+Inputs!$C$40)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="O15" s="5">
+        <f>$G$15*(N14+O14)/2/((Inputs!$C$39+Inputs!$C$40)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="5">
+        <f>$G$15*(O14+P14)/2/((Inputs!$C$39+Inputs!$C$40)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="5">
+        <f>$G$15*(P14+Q14)/2/((Inputs!$C$39+Inputs!$C$40)/2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C16" s="5">
         <v>40362</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D16" s="5">
         <v>47596</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E16" s="5">
         <v>51469</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F16" s="5">
         <v>54355</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G16" s="5">
         <v>55438</v>
       </c>
-      <c r="H9" s="5">
-        <f>G9*(1+Inputs!$C$21)+Inputs!$C$20*0.5*(G33+H33)</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="5">
-        <f>H9*(1+Inputs!$C$21)+Inputs!$C$20*0.5*(H33+I33)</f>
-        <v>0</v>
-      </c>
-      <c r="J9" s="5">
-        <f>I9*(1+Inputs!$C$21)+Inputs!$C$20*0.5*(I33+J33)</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="5">
-        <f>J9*(1+Inputs!$C$21)+Inputs!$C$20*0.5*(J33+K33)</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="5">
-        <f>K9*(1+Inputs!$C$21)+Inputs!$C$20*0.5*(K33+L33)</f>
-        <v>0</v>
-      </c>
-      <c r="M9" s="5">
-        <f>L9*(1+Inputs!$C$21)+Inputs!$C$20*0.5*(L33+M33)</f>
-        <v>0</v>
-      </c>
-      <c r="N9" s="5">
-        <f>M9*(1+Inputs!$C$21)+Inputs!$C$20*0.5*(M33+N33)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" s="5">
-        <v>4809</v>
-      </c>
-      <c r="D10" s="5">
-        <v>2561</v>
-      </c>
-      <c r="E10" s="5">
-        <v>5177</v>
-      </c>
-      <c r="F10" s="5">
-        <v>8526</v>
-      </c>
-      <c r="G10" s="5">
-        <v>2662</v>
-      </c>
-      <c r="H10" s="5">
-        <f>H8*Inputs!$C$22</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="5">
-        <f>I8*Inputs!$C$22</f>
-        <v>0</v>
-      </c>
-      <c r="J10" s="5">
-        <f>J8*Inputs!$C$22</f>
-        <v>0</v>
-      </c>
-      <c r="K10" s="5">
-        <f>K8*Inputs!$C$22</f>
-        <v>0</v>
-      </c>
-      <c r="L10" s="5">
-        <f>L8*Inputs!$C$22</f>
-        <v>0</v>
-      </c>
-      <c r="M10" s="5">
-        <f>M8*Inputs!$C$22</f>
-        <v>0</v>
-      </c>
-      <c r="N10" s="5">
-        <f>N8*Inputs!$C$22</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" s="5">
-        <v>13788</v>
-      </c>
-      <c r="D11" s="5">
-        <v>14792</v>
-      </c>
-      <c r="E11" s="5">
-        <v>16204</v>
-      </c>
-      <c r="F11" s="5">
-        <v>17401</v>
-      </c>
-      <c r="G11" s="5">
-        <v>19629</v>
-      </c>
-      <c r="H11" s="5">
-        <f>G19*Inputs!$C$23</f>
-        <v>0</v>
-      </c>
-      <c r="I11" s="5">
-        <f>H19*Inputs!$C$23</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="5">
-        <f>I19*Inputs!$C$23</f>
-        <v>0</v>
-      </c>
-      <c r="K11" s="5">
-        <f>J19*Inputs!$C$23</f>
-        <v>0</v>
-      </c>
-      <c r="L11" s="5">
-        <f>K19*Inputs!$C$23</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="5">
-        <f>L19*Inputs!$C$23</f>
-        <v>0</v>
-      </c>
-      <c r="N11" s="5">
-        <f>M19*Inputs!$C$23</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="5">
-        <v>9376</v>
-      </c>
-      <c r="D12" s="5">
-        <v>11447</v>
-      </c>
-      <c r="E12" s="5">
-        <v>12301</v>
-      </c>
-      <c r="F12" s="5">
-        <v>13282</v>
-      </c>
-      <c r="G12" s="5">
-        <v>13801</v>
-      </c>
-      <c r="H12" s="5">
-        <f>(G27+H27)/2*Inputs!$C$26</f>
-        <v>0</v>
-      </c>
-      <c r="I12" s="5">
-        <f>(H27+I27)/2*Inputs!$C$26</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="5">
-        <f>(I27+J27)/2*Inputs!$C$26</f>
-        <v>0</v>
-      </c>
-      <c r="K12" s="5">
-        <f>(J27+K27)/2*Inputs!$C$26</f>
-        <v>0</v>
-      </c>
-      <c r="L12" s="5">
-        <f>(K27+L27)/2*Inputs!$C$26</f>
-        <v>0</v>
-      </c>
-      <c r="M12" s="5">
-        <f>(L27+M27)/2*Inputs!$C$26</f>
-        <v>0</v>
-      </c>
-      <c r="N12" s="5">
-        <f>(M27+N27)/2*Inputs!$C$26</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="5">
-        <v>22007</v>
-      </c>
-      <c r="D13" s="5">
-        <v>23917</v>
-      </c>
-      <c r="E13" s="5">
-        <v>28142</v>
-      </c>
-      <c r="F13" s="5">
-        <v>32198</v>
-      </c>
-      <c r="G13" s="5">
-        <v>24669</v>
-      </c>
-      <c r="H13" s="5">
-        <f>H9+H10-H11-H12</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="5">
-        <f>I9+I10-I11-I12</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="5">
-        <f>J9+J10-J11-J12</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="5">
-        <f>K9+K10-K11-K12</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="5">
-        <f>L9+L10-L11-L12</f>
-        <v>0</v>
-      </c>
-      <c r="M13" s="5">
-        <f>M9+M10-M11-M12</f>
-        <v>0</v>
-      </c>
-      <c r="N13" s="5">
-        <f>N9+N10-N11-N12</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" s="5">
-        <v>5047</v>
-      </c>
-      <c r="D14" s="5">
-        <v>6796</v>
-      </c>
-      <c r="E14" s="5">
-        <v>6810</v>
-      </c>
-      <c r="F14" s="5">
-        <v>8245</v>
-      </c>
-      <c r="G14" s="5">
-        <v>-2877</v>
-      </c>
-      <c r="H14" s="5">
-        <f>MAX(H13,0)*Inputs!$C$7</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="5">
-        <f>MAX(I13,0)*Inputs!$C$7</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="5">
-        <f>MAX(J13,0)*Inputs!$C$7</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="5">
-        <f>MAX(K13,0)*Inputs!$C$7</f>
-        <v>0</v>
-      </c>
-      <c r="L14" s="5">
-        <f>MAX(L13,0)*Inputs!$C$7</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="5">
-        <f>MAX(M13,0)*Inputs!$C$7</f>
-        <v>0</v>
-      </c>
-      <c r="N14" s="5">
-        <f>MAX(N13,0)*Inputs!$C$7</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" s="5">
-        <v>16960</v>
-      </c>
-      <c r="D15" s="5">
-        <v>17121</v>
-      </c>
-      <c r="E15" s="5">
-        <v>21332</v>
-      </c>
-      <c r="F15" s="5">
-        <v>23953</v>
-      </c>
-      <c r="G15" s="5">
-        <v>27546</v>
-      </c>
-      <c r="H15" s="5">
-        <f>H13-H14</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="5">
-        <f>I13-I14</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="5">
-        <f>J13-J14</f>
-        <v>0</v>
-      </c>
-      <c r="K15" s="5">
-        <f>K13-K14</f>
-        <v>0</v>
-      </c>
-      <c r="L15" s="5">
-        <f>L13-L14</f>
-        <v>0</v>
-      </c>
-      <c r="M15" s="5">
-        <f>M13-M14</f>
-        <v>0</v>
-      </c>
-      <c r="N15" s="5">
-        <f>N13-N14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" s="13">
-        <f>C15/Inputs!$C$15</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="13">
-        <f>D15/Inputs!$C$15</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="13">
-        <f>E15/Inputs!$C$15</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="13">
-        <f>F15/Inputs!$C$15</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="13">
-        <f>G15/Inputs!$C$15</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="13">
-        <f>H15/Inputs!$C$15</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="13">
-        <f>I15/Inputs!$C$15</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="13">
-        <f>J15/Inputs!$C$15</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="13">
-        <f>K15/Inputs!$C$15</f>
-        <v>0</v>
-      </c>
-      <c r="L16" s="13">
-        <f>L15/Inputs!$C$15</f>
-        <v>0</v>
-      </c>
-      <c r="M16" s="13">
-        <f>M15/Inputs!$C$15</f>
-        <v>0</v>
-      </c>
-      <c r="N16" s="13">
-        <f>N15/Inputs!$C$15</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="H16" s="5">
+        <f>H15+H13</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <f>I15+I13</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <f>J15+J13</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <f>K15+K13</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <f>L15+L13</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="5">
+        <f>M15+M13</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <f>N15+N13</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="5">
+        <f>O15+O13</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="5">
+        <f>P15+P13</f>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="5">
+        <f>Q15+Q13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H17" s="5">
-        <f>MAX(H15,0)*Inputs!$C$27</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="5">
-        <f>MAX(I15,0)*Inputs!$C$27</f>
-        <v>0</v>
-      </c>
-      <c r="J17" s="5">
-        <f>MAX(J15,0)*Inputs!$C$27</f>
-        <v>0</v>
-      </c>
-      <c r="K17" s="5">
-        <f>MAX(K15,0)*Inputs!$C$27</f>
-        <v>0</v>
-      </c>
-      <c r="L17" s="5">
-        <f>MAX(L15,0)*Inputs!$C$27</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="5">
-        <f>MAX(M15,0)*Inputs!$C$27</f>
-        <v>0</v>
-      </c>
-      <c r="N17" s="5">
-        <f>MAX(N15,0)*Inputs!$C$27</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+        <v>104</v>
+      </c>
+      <c r="C17" s="6">
+        <f>C16/C19</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="6">
+        <f>D16/D19</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="6">
+        <f>E16/E19</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="6">
+        <f>F16/F19</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="6">
+        <f>G16/G19</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="6">
+        <f>H16/H19</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="6">
+        <f>I16/I19</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="6">
+        <f>J16/J19</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="6">
+        <f>K16/K19</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="6">
+        <f>L16/L19</f>
+        <v>0</v>
+      </c>
+      <c r="M17" s="6">
+        <f>M16/M19</f>
+        <v>0</v>
+      </c>
+      <c r="N17" s="6">
+        <f>N16/N19</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="6">
+        <f>O16/O19</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="6">
+        <f>P16/P19</f>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="6">
+        <f>Q16/Q19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" s="12" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
@@ -2942,589 +3424,682 @@
       <c r="L18" s="12"/>
       <c r="M18" s="12"/>
       <c r="N18" s="12"/>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="O18" s="12"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
+    </row>
+    <row r="19" spans="1:17">
       <c r="A19" s="2" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="C19" s="5">
-        <v>224923</v>
+        <v>132669</v>
       </c>
       <c r="D19" s="5">
-        <v>240424</v>
+        <v>176207</v>
       </c>
       <c r="E19" s="5">
-        <v>258934</v>
+        <v>178525</v>
       </c>
       <c r="F19" s="5">
-        <v>271437</v>
+        <v>188138</v>
       </c>
       <c r="G19" s="5">
-        <v>318697</v>
+        <v>187385</v>
       </c>
       <c r="H19" s="5">
-        <f>G19+H33-H11</f>
+        <f>H15/($G$15/($G$19-$G$12))+H12</f>
         <v>0</v>
       </c>
       <c r="I19" s="5">
-        <f>H19+I33-I11</f>
+        <f>I15/($G$15/($G$19-$G$12))+I12</f>
         <v>0</v>
       </c>
       <c r="J19" s="5">
-        <f>I19+J33-J11</f>
+        <f>J15/($G$15/($G$19-$G$12))+J12</f>
         <v>0</v>
       </c>
       <c r="K19" s="5">
-        <f>J19+K33-K11</f>
+        <f>K15/($G$15/($G$19-$G$12))+K12</f>
         <v>0</v>
       </c>
       <c r="L19" s="5">
-        <f>K19+L33-L11</f>
+        <f>L15/($G$15/($G$19-$G$12))+L12</f>
         <v>0</v>
       </c>
       <c r="M19" s="5">
-        <f>L19+M33-M11</f>
+        <f>M15/($G$15/($G$19-$G$12))+M12</f>
         <v>0</v>
       </c>
       <c r="N19" s="5">
-        <f>M19+N33-N11</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+        <f>N15/($G$15/($G$19-$G$12))+N12</f>
+        <v>0</v>
+      </c>
+      <c r="O19" s="5">
+        <f>O15/($G$15/($G$19-$G$12))+O12</f>
+        <v>0</v>
+      </c>
+      <c r="P19" s="5">
+        <f>P15/($G$15/($G$19-$G$12))+P12</f>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="5">
+        <f>Q15/($G$15/($G$19-$G$12))+Q12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
       <c r="A20" s="2" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="C20" s="5">
-        <v>91126</v>
+        <v>4809</v>
       </c>
       <c r="D20" s="5">
-        <v>89179</v>
+        <v>2561</v>
       </c>
       <c r="E20" s="5">
-        <v>87664</v>
+        <v>5177</v>
       </c>
       <c r="F20" s="5">
-        <v>100859</v>
+        <v>8526</v>
       </c>
       <c r="G20" s="5">
-        <v>84957</v>
+        <v>2662</v>
       </c>
       <c r="H20" s="5">
-        <f>G20+H32-H33</f>
+        <f>H19*Inputs!$C$30</f>
         <v>0</v>
       </c>
       <c r="I20" s="5">
-        <f>H20+I32-I33</f>
+        <f>I19*Inputs!$C$30</f>
         <v>0</v>
       </c>
       <c r="J20" s="5">
-        <f>I20+J32-J33</f>
+        <f>J19*Inputs!$C$30</f>
         <v>0</v>
       </c>
       <c r="K20" s="5">
-        <f>J20+K32-K33</f>
+        <f>K19*Inputs!$C$30</f>
         <v>0</v>
       </c>
       <c r="L20" s="5">
-        <f>K20+L32-L33</f>
+        <f>L19*Inputs!$C$30</f>
         <v>0</v>
       </c>
       <c r="M20" s="5">
-        <f>L20+M32-M33</f>
+        <f>M19*Inputs!$C$30</f>
         <v>0</v>
       </c>
       <c r="N20" s="5">
-        <f>M20+N32-N33</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+        <f>N19*Inputs!$C$30</f>
+        <v>0</v>
+      </c>
+      <c r="O20" s="5">
+        <f>O19*Inputs!$C$30</f>
+        <v>0</v>
+      </c>
+      <c r="P20" s="5">
+        <f>P19*Inputs!$C$30</f>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="5">
+        <f>Q19*Inputs!$C$30</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
       <c r="A21" s="2" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="C21" s="5">
-        <v>10626</v>
+        <v>13788</v>
       </c>
       <c r="D21" s="5">
-        <v>13935</v>
+        <v>14792</v>
       </c>
       <c r="E21" s="5">
-        <v>15885</v>
+        <v>16204</v>
       </c>
       <c r="F21" s="5">
-        <v>19704</v>
+        <v>17401</v>
       </c>
       <c r="G21" s="5">
-        <v>24180</v>
+        <v>19629</v>
       </c>
       <c r="H21" s="5">
-        <f>G21*(1+Inputs!$C$30)</f>
+        <f>G32*Inputs!$C$31</f>
         <v>0</v>
       </c>
       <c r="I21" s="5">
-        <f>H21*(1+Inputs!$C$30)</f>
+        <f>H32*Inputs!$C$31</f>
         <v>0</v>
       </c>
       <c r="J21" s="5">
-        <f>I21*(1+Inputs!$C$30)</f>
+        <f>I32*Inputs!$C$31</f>
         <v>0</v>
       </c>
       <c r="K21" s="5">
-        <f>J21*(1+Inputs!$C$30)</f>
+        <f>J32*Inputs!$C$31</f>
         <v>0</v>
       </c>
       <c r="L21" s="5">
-        <f>K21*(1+Inputs!$C$30)</f>
+        <f>K32*Inputs!$C$31</f>
         <v>0</v>
       </c>
       <c r="M21" s="5">
-        <f>L21*(1+Inputs!$C$30)</f>
+        <f>L32*Inputs!$C$31</f>
         <v>0</v>
       </c>
       <c r="N21" s="5">
-        <f>M21*(1+Inputs!$C$30)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+        <f>M32*Inputs!$C$31</f>
+        <v>0</v>
+      </c>
+      <c r="O21" s="5">
+        <f>N32*Inputs!$C$31</f>
+        <v>0</v>
+      </c>
+      <c r="P21" s="5">
+        <f>O32*Inputs!$C$31</f>
+        <v>0</v>
+      </c>
+      <c r="Q21" s="5">
+        <f>P32*Inputs!$C$31</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
       <c r="A22" s="2" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="C22" s="5">
-        <v>89156</v>
+        <v>9376</v>
       </c>
       <c r="D22" s="5">
-        <v>103651</v>
+        <v>11447</v>
       </c>
       <c r="E22" s="5">
-        <v>116795</v>
+        <v>12301</v>
       </c>
       <c r="F22" s="5">
-        <v>131733</v>
+        <v>13282</v>
       </c>
       <c r="G22" s="5">
-        <v>130609</v>
+        <v>13801</v>
       </c>
       <c r="H22" s="5">
-        <f>H8*Inputs!$C$28</f>
+        <f>(G41+H41)/2*Inputs!$C$34+G42*Inputs!$C$34</f>
         <v>0</v>
       </c>
       <c r="I22" s="5">
-        <f>I8*Inputs!$C$28</f>
+        <f>(H41+I41)/2*Inputs!$C$34+H42*Inputs!$C$34</f>
         <v>0</v>
       </c>
       <c r="J22" s="5">
-        <f>J8*Inputs!$C$28</f>
+        <f>(I41+J41)/2*Inputs!$C$34+I42*Inputs!$C$34</f>
         <v>0</v>
       </c>
       <c r="K22" s="5">
-        <f>K8*Inputs!$C$28</f>
+        <f>(J41+K41)/2*Inputs!$C$34+J42*Inputs!$C$34</f>
         <v>0</v>
       </c>
       <c r="L22" s="5">
-        <f>L8*Inputs!$C$28</f>
+        <f>(K41+L41)/2*Inputs!$C$34+K42*Inputs!$C$34</f>
         <v>0</v>
       </c>
       <c r="M22" s="5">
-        <f>M8*Inputs!$C$28</f>
+        <f>(L41+M41)/2*Inputs!$C$34+L42*Inputs!$C$34</f>
         <v>0</v>
       </c>
       <c r="N22" s="5">
-        <f>N8*Inputs!$C$28</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+        <f>(M41+N41)/2*Inputs!$C$34+M42*Inputs!$C$34</f>
+        <v>0</v>
+      </c>
+      <c r="O22" s="5">
+        <f>(N41+O41)/2*Inputs!$C$34+N42*Inputs!$C$34</f>
+        <v>0</v>
+      </c>
+      <c r="P22" s="5">
+        <f>(O41+P41)/2*Inputs!$C$34+O42*Inputs!$C$34</f>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="5">
+        <f>(P41+Q41)/2*Inputs!$C$34+P42*Inputs!$C$34</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
       <c r="A23" s="2" t="s">
-        <v>83</v>
+        <v>109</v>
+      </c>
+      <c r="C23" s="5">
+        <v>22007</v>
+      </c>
+      <c r="D23" s="5">
+        <v>23917</v>
+      </c>
+      <c r="E23" s="5">
+        <v>28142</v>
+      </c>
+      <c r="F23" s="5">
+        <v>32198</v>
       </c>
       <c r="G23" s="5">
-        <v>0</v>
+        <v>24669</v>
       </c>
       <c r="H23" s="5">
-        <f>G23+H36+H37+H38</f>
+        <f>H16+H20-H21-H22</f>
         <v>0</v>
       </c>
       <c r="I23" s="5">
-        <f>H23+I36+I37+I38</f>
+        <f>I16+I20-I21-I22</f>
         <v>0</v>
       </c>
       <c r="J23" s="5">
-        <f>I23+J36+J37+J38</f>
+        <f>J16+J20-J21-J22</f>
         <v>0</v>
       </c>
       <c r="K23" s="5">
-        <f>J23+K36+K37+K38</f>
+        <f>K16+K20-K21-K22</f>
         <v>0</v>
       </c>
       <c r="L23" s="5">
-        <f>K23+L36+L37+L38</f>
+        <f>L16+L20-L21-L22</f>
         <v>0</v>
       </c>
       <c r="M23" s="5">
-        <f>L23+M36+M37+M38</f>
+        <f>M16+M20-M21-M22</f>
         <v>0</v>
       </c>
       <c r="N23" s="5">
-        <f>M23+N36+N37+N38</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+        <f>N16+N20-N21-N22</f>
+        <v>0</v>
+      </c>
+      <c r="O23" s="5">
+        <f>O16+O20-O21-O22</f>
+        <v>0</v>
+      </c>
+      <c r="P23" s="5">
+        <f>P16+P20-P21-P22</f>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="5">
+        <f>Q16+Q20-Q21-Q22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17">
       <c r="A24" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C24" s="14">
-        <f>C19+C20+C21+C22</f>
-        <v>0</v>
-      </c>
-      <c r="D24" s="14">
-        <f>D19+D20+D21+D22</f>
-        <v>0</v>
-      </c>
-      <c r="E24" s="14">
-        <f>E19+E20+E21+E22</f>
-        <v>0</v>
-      </c>
-      <c r="F24" s="14">
-        <f>F19+F20+F21+F22</f>
-        <v>0</v>
-      </c>
-      <c r="G24" s="14">
-        <f>G19+G20+G21+G22+G23</f>
-        <v>0</v>
-      </c>
-      <c r="H24" s="14">
-        <f>H19+H20+H21+H22+H23</f>
-        <v>0</v>
-      </c>
-      <c r="I24" s="14">
-        <f>I19+I20+I21+I22+I23</f>
-        <v>0</v>
-      </c>
-      <c r="J24" s="14">
-        <f>J19+J20+J21+J22+J23</f>
-        <v>0</v>
-      </c>
-      <c r="K24" s="14">
-        <f>K19+K20+K21+K22+K23</f>
-        <v>0</v>
-      </c>
-      <c r="L24" s="14">
-        <f>L19+L20+L21+L22+L23</f>
-        <v>0</v>
-      </c>
-      <c r="M24" s="14">
-        <f>M19+M20+M21+M22+M23</f>
-        <v>0</v>
-      </c>
-      <c r="N24" s="14">
-        <f>N19+N20+N21+N22+N23</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+        <v>110</v>
+      </c>
+      <c r="C24" s="5">
+        <v>5047</v>
+      </c>
+      <c r="D24" s="5">
+        <v>6796</v>
+      </c>
+      <c r="E24" s="5">
+        <v>6810</v>
+      </c>
+      <c r="F24" s="5">
+        <v>8245</v>
+      </c>
+      <c r="G24" s="5">
+        <v>-2877</v>
+      </c>
+      <c r="H24" s="5">
+        <f>MAX(H23,0)*Inputs!$C$7</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="5">
+        <f>MAX(I23,0)*Inputs!$C$7</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="5">
+        <f>MAX(J23,0)*Inputs!$C$7</f>
+        <v>0</v>
+      </c>
+      <c r="K24" s="5">
+        <f>MAX(K23,0)*Inputs!$C$7</f>
+        <v>0</v>
+      </c>
+      <c r="L24" s="5">
+        <f>MAX(L23,0)*Inputs!$C$7</f>
+        <v>0</v>
+      </c>
+      <c r="M24" s="5">
+        <f>MAX(M23,0)*Inputs!$C$7</f>
+        <v>0</v>
+      </c>
+      <c r="N24" s="5">
+        <f>MAX(N23,0)*Inputs!$C$7</f>
+        <v>0</v>
+      </c>
+      <c r="O24" s="5">
+        <f>MAX(O23,0)*Inputs!$C$7</f>
+        <v>0</v>
+      </c>
+      <c r="P24" s="5">
+        <f>MAX(P23,0)*Inputs!$C$7</f>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="5">
+        <f>MAX(Q23,0)*Inputs!$C$7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17">
       <c r="A25" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C25" s="5">
-        <v>9697</v>
-      </c>
-      <c r="D25" s="5">
-        <v>9697</v>
-      </c>
-      <c r="E25" s="5">
-        <v>9697</v>
-      </c>
-      <c r="F25" s="5">
-        <v>9697</v>
+        <v>111</v>
       </c>
       <c r="G25" s="5">
-        <v>9697</v>
+        <f>Inputs!$C$28</f>
+        <v>0</v>
       </c>
       <c r="H25" s="5">
-        <f>G25</f>
+        <f>G25*(1+Inputs!$C$29)</f>
         <v>0</v>
       </c>
       <c r="I25" s="5">
-        <f>H25</f>
+        <f>H25*(1+Inputs!$C$29)</f>
         <v>0</v>
       </c>
       <c r="J25" s="5">
-        <f>I25</f>
+        <f>I25*(1+Inputs!$C$29)</f>
         <v>0</v>
       </c>
       <c r="K25" s="5">
-        <f>J25</f>
+        <f>J25*(1+Inputs!$C$29)</f>
         <v>0</v>
       </c>
       <c r="L25" s="5">
-        <f>K25</f>
+        <f>K25*(1+Inputs!$C$29)</f>
         <v>0</v>
       </c>
       <c r="M25" s="5">
-        <f>L25</f>
+        <f>L25*(1+Inputs!$C$29)</f>
         <v>0</v>
       </c>
       <c r="N25" s="5">
-        <f>M25</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+        <f>M25*(1+Inputs!$C$29)</f>
+        <v>0</v>
+      </c>
+      <c r="O25" s="5">
+        <f>N25*(1+Inputs!$C$29)</f>
+        <v>0</v>
+      </c>
+      <c r="P25" s="5">
+        <f>O25*(1+Inputs!$C$29)</f>
+        <v>0</v>
+      </c>
+      <c r="Q25" s="5">
+        <f>P25*(1+Inputs!$C$29)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
       <c r="A26" s="2" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="C26" s="5">
-        <v>125677</v>
+        <v>16960</v>
       </c>
       <c r="D26" s="5">
-        <v>137326</v>
+        <v>17121</v>
       </c>
       <c r="E26" s="5">
-        <v>151013</v>
+        <v>21332</v>
       </c>
       <c r="F26" s="5">
-        <v>174374</v>
+        <v>23953</v>
       </c>
       <c r="G26" s="5">
-        <v>193479</v>
+        <v>27546</v>
       </c>
       <c r="H26" s="5">
-        <f>G26+H15-H17</f>
+        <f>H23-H24+H25</f>
         <v>0</v>
       </c>
       <c r="I26" s="5">
-        <f>H26+I15-I17</f>
+        <f>I23-I24+I25</f>
         <v>0</v>
       </c>
       <c r="J26" s="5">
-        <f>I26+J15-J17</f>
+        <f>J23-J24+J25</f>
         <v>0</v>
       </c>
       <c r="K26" s="5">
-        <f>J26+K15-K17</f>
+        <f>K23-K24+K25</f>
         <v>0</v>
       </c>
       <c r="L26" s="5">
-        <f>K26+L15-L17</f>
+        <f>L23-L24+L25</f>
         <v>0</v>
       </c>
       <c r="M26" s="5">
-        <f>L26+M15-M17</f>
+        <f>M23-M24+M25</f>
         <v>0</v>
       </c>
       <c r="N26" s="5">
-        <f>M26+N15-N17</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
+        <f>N23-N24+N25</f>
+        <v>0</v>
+      </c>
+      <c r="O26" s="5">
+        <f>O23-O24+O25</f>
+        <v>0</v>
+      </c>
+      <c r="P26" s="5">
+        <f>P23-P24+P25</f>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="5">
+        <f>Q23-Q24+Q25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17">
       <c r="A27" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C27" s="5">
-        <v>210707</v>
-      </c>
-      <c r="D27" s="5">
-        <v>222913</v>
-      </c>
-      <c r="E27" s="5">
-        <v>237131</v>
-      </c>
-      <c r="F27" s="5">
-        <v>250096</v>
-      </c>
-      <c r="G27" s="5">
-        <v>271005</v>
+        <v>113</v>
       </c>
       <c r="H27" s="5">
-        <f>G27+H32*Inputs!$C$25</f>
+        <f>(H23-H24)*(Inputs!$C$18/($G38+$G39+Inputs!$C$18))</f>
         <v>0</v>
       </c>
       <c r="I27" s="5">
-        <f>H27+I32*Inputs!$C$25</f>
+        <f>(I23-I24)*(Inputs!$C$18/($G38+$G39+Inputs!$C$18))</f>
         <v>0</v>
       </c>
       <c r="J27" s="5">
-        <f>I27+J32*Inputs!$C$25</f>
+        <f>(J23-J24)*(Inputs!$C$18/($G38+$G39+Inputs!$C$18))</f>
         <v>0</v>
       </c>
       <c r="K27" s="5">
-        <f>J27+K32*Inputs!$C$25</f>
+        <f>(K23-K24)*(Inputs!$C$18/($G38+$G39+Inputs!$C$18))</f>
         <v>0</v>
       </c>
       <c r="L27" s="5">
-        <f>K27+L32*Inputs!$C$25</f>
+        <f>(L23-L24)*(Inputs!$C$18/($G38+$G39+Inputs!$C$18))</f>
         <v>0</v>
       </c>
       <c r="M27" s="5">
-        <f>L27+M32*Inputs!$C$25</f>
+        <f>(M23-M24)*(Inputs!$C$18/($G38+$G39+Inputs!$C$18))</f>
         <v>0</v>
       </c>
       <c r="N27" s="5">
-        <f>M27+N32*Inputs!$C$25</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
+        <f>(N23-N24)*(Inputs!$C$18/($G38+$G39+Inputs!$C$18))</f>
+        <v>0</v>
+      </c>
+      <c r="O27" s="5">
+        <f>(O23-O24)*(Inputs!$C$18/($G38+$G39+Inputs!$C$18))</f>
+        <v>0</v>
+      </c>
+      <c r="P27" s="5">
+        <f>(P23-P24)*(Inputs!$C$18/($G38+$G39+Inputs!$C$18))</f>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="5">
+        <f>(Q23-Q24)*(Inputs!$C$18/($G38+$G39+Inputs!$C$18))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17">
       <c r="A28" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" s="5">
-        <v>69751</v>
-      </c>
-      <c r="D28" s="5">
-        <v>77253</v>
-      </c>
-      <c r="E28" s="5">
-        <v>81437</v>
-      </c>
-      <c r="F28" s="5">
-        <v>89565</v>
-      </c>
-      <c r="G28" s="5">
-        <v>84262</v>
+        <v>114</v>
       </c>
       <c r="H28" s="5">
-        <f>H8*Inputs!$C$29</f>
+        <f>H26-H27</f>
         <v>0</v>
       </c>
       <c r="I28" s="5">
-        <f>I8*Inputs!$C$29</f>
+        <f>I26-I27</f>
         <v>0</v>
       </c>
       <c r="J28" s="5">
-        <f>J8*Inputs!$C$29</f>
+        <f>J26-J27</f>
         <v>0</v>
       </c>
       <c r="K28" s="5">
-        <f>K8*Inputs!$C$29</f>
+        <f>K26-K27</f>
         <v>0</v>
       </c>
       <c r="L28" s="5">
-        <f>L8*Inputs!$C$29</f>
+        <f>L26-L27</f>
         <v>0</v>
       </c>
       <c r="M28" s="5">
-        <f>M8*Inputs!$C$29</f>
+        <f>M26-M27</f>
         <v>0</v>
       </c>
       <c r="N28" s="5">
-        <f>N8*Inputs!$C$29</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
+        <f>N26-N27</f>
+        <v>0</v>
+      </c>
+      <c r="O28" s="5">
+        <f>O26-O27</f>
+        <v>0</v>
+      </c>
+      <c r="P28" s="5">
+        <f>P26-P27</f>
+        <v>0</v>
+      </c>
+      <c r="Q28" s="5">
+        <f>Q26-Q27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17">
       <c r="A29" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C29" s="14">
-        <f>C25+C26+C27+C28</f>
-        <v>0</v>
-      </c>
-      <c r="D29" s="14">
-        <f>D25+D26+D27+D28</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="14">
-        <f>E25+E26+E27+E28</f>
-        <v>0</v>
-      </c>
-      <c r="F29" s="14">
-        <f>F25+F26+F27+F28</f>
-        <v>0</v>
-      </c>
-      <c r="G29" s="14">
-        <f>G25+G26+G27+G28</f>
-        <v>0</v>
-      </c>
-      <c r="H29" s="14">
-        <f>H25+H26+H27+H28</f>
-        <v>0</v>
-      </c>
-      <c r="I29" s="14">
-        <f>I25+I26+I27+I28</f>
-        <v>0</v>
-      </c>
-      <c r="J29" s="14">
-        <f>J25+J26+J27+J28</f>
-        <v>0</v>
-      </c>
-      <c r="K29" s="14">
-        <f>K25+K26+K27+K28</f>
-        <v>0</v>
-      </c>
-      <c r="L29" s="14">
-        <f>L25+L26+L27+L28</f>
-        <v>0</v>
-      </c>
-      <c r="M29" s="14">
-        <f>M25+M26+M27+M28</f>
-        <v>0</v>
-      </c>
-      <c r="N29" s="14">
-        <f>N25+N26+N27+N28</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
+        <v>115</v>
+      </c>
+      <c r="C29" s="13">
+        <f>C26/Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+      <c r="D29" s="13">
+        <f>D26/Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="13">
+        <f>E26/Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="13">
+        <f>F26/Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="13">
+        <f>G26/Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+      <c r="H29" s="13">
+        <f>H28/Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="13">
+        <f>I28/Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+      <c r="J29" s="13">
+        <f>J28/Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="13">
+        <f>K28/Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+      <c r="L29" s="13">
+        <f>L28/Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+      <c r="M29" s="13">
+        <f>M28/Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+      <c r="N29" s="13">
+        <f>N28/Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+      <c r="O29" s="13">
+        <f>O28/Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+      <c r="P29" s="13">
+        <f>P28/Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+      <c r="Q29" s="13">
+        <f>Q28/Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17">
       <c r="A30" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H30" s="5">
+        <f>MAX(H28,0)*Inputs!$C$35</f>
+        <v>0</v>
+      </c>
+      <c r="I30" s="5">
+        <f>MAX(I28,0)*Inputs!$C$35</f>
+        <v>0</v>
+      </c>
+      <c r="J30" s="5">
+        <f>MAX(J28,0)*Inputs!$C$35</f>
+        <v>0</v>
+      </c>
+      <c r="K30" s="5">
+        <f>MAX(K28,0)*Inputs!$C$35</f>
+        <v>0</v>
+      </c>
+      <c r="L30" s="5">
+        <f>MAX(L28,0)*Inputs!$C$35</f>
+        <v>0</v>
+      </c>
+      <c r="M30" s="5">
+        <f>MAX(M28,0)*Inputs!$C$35</f>
+        <v>0</v>
+      </c>
+      <c r="N30" s="5">
+        <f>MAX(N28,0)*Inputs!$C$35</f>
+        <v>0</v>
+      </c>
+      <c r="O30" s="5">
+        <f>MAX(O28,0)*Inputs!$C$35</f>
+        <v>0</v>
+      </c>
+      <c r="P30" s="5">
+        <f>MAX(P28,0)*Inputs!$C$35</f>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="5">
+        <f>MAX(Q28,0)*Inputs!$C$35</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17">
+      <c r="A31" s="12" t="s">
         <v>90</v>
-      </c>
-      <c r="C30" s="15">
-        <f>IF(ABS(C24-C29)&lt;2,0,C24-C29)</f>
-        <v>0</v>
-      </c>
-      <c r="D30" s="15">
-        <f>IF(ABS(D24-D29)&lt;2,0,D24-D29)</f>
-        <v>0</v>
-      </c>
-      <c r="E30" s="15">
-        <f>IF(ABS(E24-E29)&lt;2,0,E24-E29)</f>
-        <v>0</v>
-      </c>
-      <c r="F30" s="15">
-        <f>IF(ABS(F24-F29)&lt;2,0,F24-F29)</f>
-        <v>0</v>
-      </c>
-      <c r="G30" s="15">
-        <f>IF(ABS(G24-G29)&lt;2,0,G24-G29)</f>
-        <v>0</v>
-      </c>
-      <c r="H30" s="15">
-        <f>ROUND(H24-H29,4)</f>
-        <v>0</v>
-      </c>
-      <c r="I30" s="15">
-        <f>ROUND(I24-I29,4)</f>
-        <v>0</v>
-      </c>
-      <c r="J30" s="15">
-        <f>ROUND(J24-J29,4)</f>
-        <v>0</v>
-      </c>
-      <c r="K30" s="15">
-        <f>ROUND(K24-K29,4)</f>
-        <v>0</v>
-      </c>
-      <c r="L30" s="15">
-        <f>ROUND(L24-L29,4)</f>
-        <v>0</v>
-      </c>
-      <c r="M30" s="15">
-        <f>ROUND(M24-M29,4)</f>
-        <v>0</v>
-      </c>
-      <c r="N30" s="15">
-        <f>ROUND(N24-N29,4)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
-      <c r="A31" s="12" t="s">
-        <v>64</v>
       </c>
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
@@ -3539,399 +4114,1343 @@
       <c r="L31" s="12"/>
       <c r="M31" s="12"/>
       <c r="N31" s="12"/>
-    </row>
-    <row r="32" spans="1:14">
+      <c r="O31" s="12"/>
+      <c r="P31" s="12"/>
+      <c r="Q31" s="12"/>
+    </row>
+    <row r="32" spans="1:17">
       <c r="A32" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C32" s="5">
+        <v>224923</v>
+      </c>
+      <c r="D32" s="5">
+        <v>240424</v>
+      </c>
+      <c r="E32" s="5">
+        <v>258934</v>
+      </c>
+      <c r="F32" s="5">
+        <v>271437</v>
+      </c>
+      <c r="G32" s="5">
+        <v>318697</v>
+      </c>
+      <c r="H32" s="5">
+        <f>G32+H7-H21</f>
+        <v>0</v>
+      </c>
+      <c r="I32" s="5">
+        <f>H32+I7-I21</f>
+        <v>0</v>
+      </c>
+      <c r="J32" s="5">
+        <f>I32+J7-J21</f>
+        <v>0</v>
+      </c>
+      <c r="K32" s="5">
+        <f>J32+K7-K21</f>
+        <v>0</v>
+      </c>
+      <c r="L32" s="5">
+        <f>K32+L7-L21</f>
+        <v>0</v>
+      </c>
+      <c r="M32" s="5">
+        <f>L32+M7-M21</f>
+        <v>0</v>
+      </c>
+      <c r="N32" s="5">
+        <f>M32+N7-N21</f>
+        <v>0</v>
+      </c>
+      <c r="O32" s="5">
+        <f>N32+O7-O21</f>
+        <v>0</v>
+      </c>
+      <c r="P32" s="5">
+        <f>O32+P7-P21</f>
+        <v>0</v>
+      </c>
+      <c r="Q32" s="5">
+        <f>P32+Q7-Q21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17">
+      <c r="A33" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C33" s="5">
+        <v>91126</v>
+      </c>
+      <c r="D33" s="5">
+        <v>89179</v>
+      </c>
+      <c r="E33" s="5">
+        <v>87664</v>
+      </c>
+      <c r="F33" s="5">
+        <v>100859</v>
+      </c>
+      <c r="G33" s="5">
+        <v>84957</v>
+      </c>
+      <c r="H33" s="5">
+        <f>G33+H6-H7</f>
+        <v>0</v>
+      </c>
+      <c r="I33" s="5">
+        <f>H33+I6-I7</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="5">
+        <f>I33+J6-J7</f>
+        <v>0</v>
+      </c>
+      <c r="K33" s="5">
+        <f>J33+K6-K7</f>
+        <v>0</v>
+      </c>
+      <c r="L33" s="5">
+        <f>K33+L6-L7</f>
+        <v>0</v>
+      </c>
+      <c r="M33" s="5">
+        <f>L33+M6-M7</f>
+        <v>0</v>
+      </c>
+      <c r="N33" s="5">
+        <f>M33+N6-N7</f>
+        <v>0</v>
+      </c>
+      <c r="O33" s="5">
+        <f>N33+O6-O7</f>
+        <v>0</v>
+      </c>
+      <c r="P33" s="5">
+        <f>O33+P6-P7</f>
+        <v>0</v>
+      </c>
+      <c r="Q33" s="5">
+        <f>P33+Q6-Q7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17">
+      <c r="A34" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C34" s="5">
+        <v>10626</v>
+      </c>
+      <c r="D34" s="5">
+        <v>13935</v>
+      </c>
+      <c r="E34" s="5">
+        <v>15885</v>
+      </c>
+      <c r="F34" s="5">
+        <v>19704</v>
+      </c>
+      <c r="G34" s="5">
+        <v>24180</v>
+      </c>
+      <c r="H34" s="5">
+        <f>G34*(1+Inputs!$C$38)+H25</f>
+        <v>0</v>
+      </c>
+      <c r="I34" s="5">
+        <f>H34*(1+Inputs!$C$38)+I25</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="5">
+        <f>I34*(1+Inputs!$C$38)+J25</f>
+        <v>0</v>
+      </c>
+      <c r="K34" s="5">
+        <f>J34*(1+Inputs!$C$38)+K25</f>
+        <v>0</v>
+      </c>
+      <c r="L34" s="5">
+        <f>K34*(1+Inputs!$C$38)+L25</f>
+        <v>0</v>
+      </c>
+      <c r="M34" s="5">
+        <f>L34*(1+Inputs!$C$38)+M25</f>
+        <v>0</v>
+      </c>
+      <c r="N34" s="5">
+        <f>M34*(1+Inputs!$C$38)+N25</f>
+        <v>0</v>
+      </c>
+      <c r="O34" s="5">
+        <f>N34*(1+Inputs!$C$38)+O25</f>
+        <v>0</v>
+      </c>
+      <c r="P34" s="5">
+        <f>O34*(1+Inputs!$C$38)+P25</f>
+        <v>0</v>
+      </c>
+      <c r="Q34" s="5">
+        <f>P34*(1+Inputs!$C$38)+Q25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17">
+      <c r="A35" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C35" s="5">
+        <v>89156</v>
+      </c>
+      <c r="D35" s="5">
+        <v>103651</v>
+      </c>
+      <c r="E35" s="5">
+        <v>116795</v>
+      </c>
+      <c r="F35" s="5">
+        <v>131733</v>
+      </c>
+      <c r="G35" s="5">
+        <v>130609</v>
+      </c>
+      <c r="H35" s="5">
+        <f>H19*Inputs!$C$36</f>
+        <v>0</v>
+      </c>
+      <c r="I35" s="5">
+        <f>I19*Inputs!$C$36</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="5">
+        <f>J19*Inputs!$C$36</f>
+        <v>0</v>
+      </c>
+      <c r="K35" s="5">
+        <f>K19*Inputs!$C$36</f>
+        <v>0</v>
+      </c>
+      <c r="L35" s="5">
+        <f>L19*Inputs!$C$36</f>
+        <v>0</v>
+      </c>
+      <c r="M35" s="5">
+        <f>M19*Inputs!$C$36</f>
+        <v>0</v>
+      </c>
+      <c r="N35" s="5">
+        <f>N19*Inputs!$C$36</f>
+        <v>0</v>
+      </c>
+      <c r="O35" s="5">
+        <f>O19*Inputs!$C$36</f>
+        <v>0</v>
+      </c>
+      <c r="P35" s="5">
+        <f>P19*Inputs!$C$36</f>
+        <v>0</v>
+      </c>
+      <c r="Q35" s="5">
+        <f>Q19*Inputs!$C$36</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17">
+      <c r="A36" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G36" s="5">
+        <v>0</v>
+      </c>
+      <c r="H36" s="5">
+        <f>H51+H52</f>
+        <v>0</v>
+      </c>
+      <c r="I36" s="5">
+        <f>I51+I52</f>
+        <v>0</v>
+      </c>
+      <c r="J36" s="5">
+        <f>J51+J52</f>
+        <v>0</v>
+      </c>
+      <c r="K36" s="5">
+        <f>K51+K52</f>
+        <v>0</v>
+      </c>
+      <c r="L36" s="5">
+        <f>L51+L52</f>
+        <v>0</v>
+      </c>
+      <c r="M36" s="5">
+        <f>M51+M52</f>
+        <v>0</v>
+      </c>
+      <c r="N36" s="5">
+        <f>N51+N52</f>
+        <v>0</v>
+      </c>
+      <c r="O36" s="5">
+        <f>O51+O52</f>
+        <v>0</v>
+      </c>
+      <c r="P36" s="5">
+        <f>P51+P52</f>
+        <v>0</v>
+      </c>
+      <c r="Q36" s="5">
+        <f>Q51+Q52</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17">
+      <c r="A37" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C37" s="14">
+        <f>C32+C33+C34+C35</f>
+        <v>0</v>
+      </c>
+      <c r="D37" s="14">
+        <f>D32+D33+D34+D35</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="14">
+        <f>E32+E33+E34+E35</f>
+        <v>0</v>
+      </c>
+      <c r="F37" s="14">
+        <f>F32+F33+F34+F35</f>
+        <v>0</v>
+      </c>
+      <c r="G37" s="14">
+        <f>G32+G33+G34+G35+G36</f>
+        <v>0</v>
+      </c>
+      <c r="H37" s="14">
+        <f>H32+H33+H34+H35+H36</f>
+        <v>0</v>
+      </c>
+      <c r="I37" s="14">
+        <f>I32+I33+I34+I35+I36</f>
+        <v>0</v>
+      </c>
+      <c r="J37" s="14">
+        <f>J32+J33+J34+J35+J36</f>
+        <v>0</v>
+      </c>
+      <c r="K37" s="14">
+        <f>K32+K33+K34+K35+K36</f>
+        <v>0</v>
+      </c>
+      <c r="L37" s="14">
+        <f>L32+L33+L34+L35+L36</f>
+        <v>0</v>
+      </c>
+      <c r="M37" s="14">
+        <f>M32+M33+M34+M35+M36</f>
+        <v>0</v>
+      </c>
+      <c r="N37" s="14">
+        <f>N32+N33+N34+N35+N36</f>
+        <v>0</v>
+      </c>
+      <c r="O37" s="14">
+        <f>O32+O33+O34+O35+O36</f>
+        <v>0</v>
+      </c>
+      <c r="P37" s="14">
+        <f>P32+P33+P34+P35+P36</f>
+        <v>0</v>
+      </c>
+      <c r="Q37" s="14">
+        <f>Q32+Q33+Q34+Q35+Q36</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17">
+      <c r="A38" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C38" s="5">
+        <v>9697</v>
+      </c>
+      <c r="D38" s="5">
+        <v>9697</v>
+      </c>
+      <c r="E38" s="5">
+        <v>9697</v>
+      </c>
+      <c r="F38" s="5">
+        <v>9697</v>
+      </c>
+      <c r="G38" s="5">
+        <v>9697</v>
+      </c>
+      <c r="H38" s="5">
+        <f>G38</f>
+        <v>0</v>
+      </c>
+      <c r="I38" s="5">
+        <f>H38</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="5">
+        <f>I38</f>
+        <v>0</v>
+      </c>
+      <c r="K38" s="5">
+        <f>J38</f>
+        <v>0</v>
+      </c>
+      <c r="L38" s="5">
+        <f>K38</f>
+        <v>0</v>
+      </c>
+      <c r="M38" s="5">
+        <f>L38</f>
+        <v>0</v>
+      </c>
+      <c r="N38" s="5">
+        <f>M38</f>
+        <v>0</v>
+      </c>
+      <c r="O38" s="5">
+        <f>N38</f>
+        <v>0</v>
+      </c>
+      <c r="P38" s="5">
+        <f>O38</f>
+        <v>0</v>
+      </c>
+      <c r="Q38" s="5">
+        <f>P38</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17">
+      <c r="A39" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C39" s="5">
+        <v>125677</v>
+      </c>
+      <c r="D39" s="5">
+        <v>137326</v>
+      </c>
+      <c r="E39" s="5">
+        <v>151013</v>
+      </c>
+      <c r="F39" s="5">
+        <v>174374</v>
+      </c>
+      <c r="G39" s="5">
+        <v>193479</v>
+      </c>
+      <c r="H39" s="5">
+        <f>G39+H28-H30</f>
+        <v>0</v>
+      </c>
+      <c r="I39" s="5">
+        <f>H39+I28-I30</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="5">
+        <f>I39+J28-J30</f>
+        <v>0</v>
+      </c>
+      <c r="K39" s="5">
+        <f>J39+K28-K30</f>
+        <v>0</v>
+      </c>
+      <c r="L39" s="5">
+        <f>K39+L28-L30</f>
+        <v>0</v>
+      </c>
+      <c r="M39" s="5">
+        <f>L39+M28-M30</f>
+        <v>0</v>
+      </c>
+      <c r="N39" s="5">
+        <f>M39+N28-N30</f>
+        <v>0</v>
+      </c>
+      <c r="O39" s="5">
+        <f>N39+O28-O30</f>
+        <v>0</v>
+      </c>
+      <c r="P39" s="5">
+        <f>O39+P28-P30</f>
+        <v>0</v>
+      </c>
+      <c r="Q39" s="5">
+        <f>P39+Q28-Q30</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17">
+      <c r="A40" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G40" s="5">
+        <f>Inputs!$C$18</f>
+        <v>0</v>
+      </c>
+      <c r="H40" s="5">
+        <f>G40+H27</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="5">
+        <f>H40+I27</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="5">
+        <f>I40+J27</f>
+        <v>0</v>
+      </c>
+      <c r="K40" s="5">
+        <f>J40+K27</f>
+        <v>0</v>
+      </c>
+      <c r="L40" s="5">
+        <f>K40+L27</f>
+        <v>0</v>
+      </c>
+      <c r="M40" s="5">
+        <f>L40+M27</f>
+        <v>0</v>
+      </c>
+      <c r="N40" s="5">
+        <f>M40+N27</f>
+        <v>0</v>
+      </c>
+      <c r="O40" s="5">
+        <f>N40+O27</f>
+        <v>0</v>
+      </c>
+      <c r="P40" s="5">
+        <f>O40+P27</f>
+        <v>0</v>
+      </c>
+      <c r="Q40" s="5">
+        <f>P40+Q27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17">
+      <c r="A41" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C41" s="5">
+        <v>210707</v>
+      </c>
+      <c r="D41" s="5">
+        <v>222913</v>
+      </c>
+      <c r="E41" s="5">
+        <v>237131</v>
+      </c>
+      <c r="F41" s="5">
+        <v>250096</v>
+      </c>
+      <c r="G41" s="5">
+        <v>271005</v>
+      </c>
+      <c r="H41" s="5">
+        <f>G41+H6*Inputs!$C$33</f>
+        <v>0</v>
+      </c>
+      <c r="I41" s="5">
+        <f>H41+I6*Inputs!$C$33</f>
+        <v>0</v>
+      </c>
+      <c r="J41" s="5">
+        <f>I41+J6*Inputs!$C$33</f>
+        <v>0</v>
+      </c>
+      <c r="K41" s="5">
+        <f>J41+K6*Inputs!$C$33</f>
+        <v>0</v>
+      </c>
+      <c r="L41" s="5">
+        <f>K41+L6*Inputs!$C$33</f>
+        <v>0</v>
+      </c>
+      <c r="M41" s="5">
+        <f>L41+M6*Inputs!$C$33</f>
+        <v>0</v>
+      </c>
+      <c r="N41" s="5">
+        <f>M41+N6*Inputs!$C$33</f>
+        <v>0</v>
+      </c>
+      <c r="O41" s="5">
+        <f>N41+O6*Inputs!$C$33</f>
+        <v>0</v>
+      </c>
+      <c r="P41" s="5">
+        <f>O41+P6*Inputs!$C$33</f>
+        <v>0</v>
+      </c>
+      <c r="Q41" s="5">
+        <f>P41+Q6*Inputs!$C$33</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17">
+      <c r="A42" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G42" s="5">
+        <v>0</v>
+      </c>
+      <c r="H42" s="5">
+        <f>G42+H52</f>
+        <v>0</v>
+      </c>
+      <c r="I42" s="5">
+        <f>H42+I52</f>
+        <v>0</v>
+      </c>
+      <c r="J42" s="5">
+        <f>I42+J52</f>
+        <v>0</v>
+      </c>
+      <c r="K42" s="5">
+        <f>J42+K52</f>
+        <v>0</v>
+      </c>
+      <c r="L42" s="5">
+        <f>K42+L52</f>
+        <v>0</v>
+      </c>
+      <c r="M42" s="5">
+        <f>L42+M52</f>
+        <v>0</v>
+      </c>
+      <c r="N42" s="5">
+        <f>M42+N52</f>
+        <v>0</v>
+      </c>
+      <c r="O42" s="5">
+        <f>N42+O52</f>
+        <v>0</v>
+      </c>
+      <c r="P42" s="5">
+        <f>O42+P52</f>
+        <v>0</v>
+      </c>
+      <c r="Q42" s="5">
+        <f>P42+Q52</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17">
+      <c r="A43" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C43" s="5">
+        <v>69751</v>
+      </c>
+      <c r="D43" s="5">
+        <v>77253</v>
+      </c>
+      <c r="E43" s="5">
+        <v>81437</v>
+      </c>
+      <c r="F43" s="5">
+        <v>89565</v>
+      </c>
+      <c r="G43" s="5">
+        <f>84262.0-Inputs!$C$18</f>
+        <v>0</v>
+      </c>
+      <c r="H43" s="5">
+        <f>H19*Inputs!$C$37</f>
+        <v>0</v>
+      </c>
+      <c r="I43" s="5">
+        <f>I19*Inputs!$C$37</f>
+        <v>0</v>
+      </c>
+      <c r="J43" s="5">
+        <f>J19*Inputs!$C$37</f>
+        <v>0</v>
+      </c>
+      <c r="K43" s="5">
+        <f>K19*Inputs!$C$37</f>
+        <v>0</v>
+      </c>
+      <c r="L43" s="5">
+        <f>L19*Inputs!$C$37</f>
+        <v>0</v>
+      </c>
+      <c r="M43" s="5">
+        <f>M19*Inputs!$C$37</f>
+        <v>0</v>
+      </c>
+      <c r="N43" s="5">
+        <f>N19*Inputs!$C$37</f>
+        <v>0</v>
+      </c>
+      <c r="O43" s="5">
+        <f>O19*Inputs!$C$37</f>
+        <v>0</v>
+      </c>
+      <c r="P43" s="5">
+        <f>P19*Inputs!$C$37</f>
+        <v>0</v>
+      </c>
+      <c r="Q43" s="5">
+        <f>Q19*Inputs!$C$37</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17">
+      <c r="A44" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C44" s="14">
+        <f>C38+C39+C40+C41+C42+C43</f>
+        <v>0</v>
+      </c>
+      <c r="D44" s="14">
+        <f>D38+D39+D40+D41+D42+D43</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="14">
+        <f>E38+E39+E40+E41+E42+E43</f>
+        <v>0</v>
+      </c>
+      <c r="F44" s="14">
+        <f>F38+F39+F40+F41+F42+F43</f>
+        <v>0</v>
+      </c>
+      <c r="G44" s="14">
+        <f>G38+G39+G40+G41+G42+G43</f>
+        <v>0</v>
+      </c>
+      <c r="H44" s="14">
+        <f>H38+H39+H40+H41+H42+H43</f>
+        <v>0</v>
+      </c>
+      <c r="I44" s="14">
+        <f>I38+I39+I40+I41+I42+I43</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="14">
+        <f>J38+J39+J40+J41+J42+J43</f>
+        <v>0</v>
+      </c>
+      <c r="K44" s="14">
+        <f>K38+K39+K40+K41+K42+K43</f>
+        <v>0</v>
+      </c>
+      <c r="L44" s="14">
+        <f>L38+L39+L40+L41+L42+L43</f>
+        <v>0</v>
+      </c>
+      <c r="M44" s="14">
+        <f>M38+M39+M40+M41+M42+M43</f>
+        <v>0</v>
+      </c>
+      <c r="N44" s="14">
+        <f>N38+N39+N40+N41+N42+N43</f>
+        <v>0</v>
+      </c>
+      <c r="O44" s="14">
+        <f>O38+O39+O40+O41+O42+O43</f>
+        <v>0</v>
+      </c>
+      <c r="P44" s="14">
+        <f>P38+P39+P40+P41+P42+P43</f>
+        <v>0</v>
+      </c>
+      <c r="Q44" s="14">
+        <f>Q38+Q39+Q40+Q41+Q42+Q43</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17">
+      <c r="A45" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C45" s="15">
+        <f>IF(ABS(C37-C44)&lt;2,0,C37-C44)</f>
+        <v>0</v>
+      </c>
+      <c r="D45" s="15">
+        <f>IF(ABS(D37-D44)&lt;2,0,D37-D44)</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="15">
+        <f>IF(ABS(E37-E44)&lt;2,0,E37-E44)</f>
+        <v>0</v>
+      </c>
+      <c r="F45" s="15">
+        <f>IF(ABS(F37-F44)&lt;2,0,F37-F44)</f>
+        <v>0</v>
+      </c>
+      <c r="G45" s="15">
+        <f>IF(ABS(G37-G44)&lt;2,0,G37-G44)</f>
+        <v>0</v>
+      </c>
+      <c r="H45" s="15">
+        <f>ROUND(H37-H44,4)</f>
+        <v>0</v>
+      </c>
+      <c r="I45" s="15">
+        <f>ROUND(I37-I44,4)</f>
+        <v>0</v>
+      </c>
+      <c r="J45" s="15">
+        <f>ROUND(J37-J44,4)</f>
+        <v>0</v>
+      </c>
+      <c r="K45" s="15">
+        <f>ROUND(K37-K44,4)</f>
+        <v>0</v>
+      </c>
+      <c r="L45" s="15">
+        <f>ROUND(L37-L44,4)</f>
+        <v>0</v>
+      </c>
+      <c r="M45" s="15">
+        <f>ROUND(M37-M44,4)</f>
+        <v>0</v>
+      </c>
+      <c r="N45" s="15">
+        <f>ROUND(N37-N44,4)</f>
+        <v>0</v>
+      </c>
+      <c r="O45" s="15">
+        <f>ROUND(O37-O44,4)</f>
+        <v>0</v>
+      </c>
+      <c r="P45" s="15">
+        <f>ROUND(P37-P44,4)</f>
+        <v>0</v>
+      </c>
+      <c r="Q45" s="15">
+        <f>ROUND(Q37-Q44,4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17">
+      <c r="A46" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="C32" s="5">
-        <v>29086</v>
-      </c>
-      <c r="D32" s="5">
-        <v>28346</v>
-      </c>
-      <c r="E32" s="5">
-        <v>33199</v>
-      </c>
-      <c r="F32" s="5">
-        <v>43099</v>
-      </c>
-      <c r="G32" s="5">
-        <v>50987</v>
-      </c>
-      <c r="H32" s="5">
-        <f>H5*Inputs!$C$19</f>
-        <v>0</v>
-      </c>
-      <c r="I32" s="5">
-        <f>I5*Inputs!$C$19</f>
-        <v>0</v>
-      </c>
-      <c r="J32" s="5">
-        <f>J5*Inputs!$C$19</f>
-        <v>0</v>
-      </c>
-      <c r="K32" s="5">
-        <f>K5*Inputs!$C$19</f>
-        <v>0</v>
-      </c>
-      <c r="L32" s="5">
-        <f>L5*Inputs!$C$19</f>
-        <v>0</v>
-      </c>
-      <c r="M32" s="5">
-        <f>M5*Inputs!$C$19</f>
-        <v>0</v>
-      </c>
-      <c r="N32" s="5">
-        <f>N5*Inputs!$C$19</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14">
-      <c r="A33" s="2" t="s">
+      <c r="B46" s="12"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="12"/>
+      <c r="K46" s="12"/>
+      <c r="L46" s="12"/>
+      <c r="M46" s="12"/>
+      <c r="N46" s="12"/>
+      <c r="O46" s="12"/>
+      <c r="P46" s="12"/>
+      <c r="Q46" s="12"/>
+    </row>
+    <row r="47" spans="1:17">
+      <c r="A47" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H47" s="5">
+        <f>(H35-H43)-(G35-G43)</f>
+        <v>0</v>
+      </c>
+      <c r="I47" s="5">
+        <f>(I35-I43)-(H35-H43)</f>
+        <v>0</v>
+      </c>
+      <c r="J47" s="5">
+        <f>(J35-J43)-(I35-I43)</f>
+        <v>0</v>
+      </c>
+      <c r="K47" s="5">
+        <f>(K35-K43)-(J35-J43)</f>
+        <v>0</v>
+      </c>
+      <c r="L47" s="5">
+        <f>(L35-L43)-(K35-K43)</f>
+        <v>0</v>
+      </c>
+      <c r="M47" s="5">
+        <f>(M35-M43)-(L35-L43)</f>
+        <v>0</v>
+      </c>
+      <c r="N47" s="5">
+        <f>(N35-N43)-(M35-M43)</f>
+        <v>0</v>
+      </c>
+      <c r="O47" s="5">
+        <f>(O35-O43)-(N35-N43)</f>
+        <v>0</v>
+      </c>
+      <c r="P47" s="5">
+        <f>(P35-P43)-(O35-O43)</f>
+        <v>0</v>
+      </c>
+      <c r="Q47" s="5">
+        <f>(Q35-Q43)-(P35-P43)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17">
+      <c r="A48" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C48" s="5">
+        <v>41788</v>
+      </c>
+      <c r="D48" s="5">
+        <v>47152</v>
+      </c>
+      <c r="E48" s="5">
+        <v>40099</v>
+      </c>
+      <c r="F48" s="5">
+        <v>50488</v>
+      </c>
+      <c r="G48" s="5">
+        <v>50902</v>
+      </c>
+      <c r="H48" s="5">
+        <f>H26-H25+H21-H47</f>
+        <v>0</v>
+      </c>
+      <c r="I48" s="5">
+        <f>I26-I25+I21-I47</f>
+        <v>0</v>
+      </c>
+      <c r="J48" s="5">
+        <f>J26-J25+J21-J47</f>
+        <v>0</v>
+      </c>
+      <c r="K48" s="5">
+        <f>K26-K25+K21-K47</f>
+        <v>0</v>
+      </c>
+      <c r="L48" s="5">
+        <f>L26-L25+L21-L47</f>
+        <v>0</v>
+      </c>
+      <c r="M48" s="5">
+        <f>M26-M25+M21-M47</f>
+        <v>0</v>
+      </c>
+      <c r="N48" s="5">
+        <f>N26-N25+N21-N47</f>
+        <v>0</v>
+      </c>
+      <c r="O48" s="5">
+        <f>O26-O25+O21-O47</f>
+        <v>0</v>
+      </c>
+      <c r="P48" s="5">
+        <f>P26-P25+P21-P47</f>
+        <v>0</v>
+      </c>
+      <c r="Q48" s="5">
+        <f>Q26-Q25+Q21-Q47</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17">
+      <c r="A49" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C49" s="5">
+        <v>-22891</v>
+      </c>
+      <c r="D49" s="5">
+        <v>-26145</v>
+      </c>
+      <c r="E49" s="5">
+        <v>-31456</v>
+      </c>
+      <c r="F49" s="5">
+        <v>-45852</v>
+      </c>
+      <c r="G49" s="5">
+        <v>-37578</v>
+      </c>
+      <c r="H49" s="5">
+        <f>-H6-G34*Inputs!$C$38</f>
+        <v>0</v>
+      </c>
+      <c r="I49" s="5">
+        <f>-I6-H34*Inputs!$C$38</f>
+        <v>0</v>
+      </c>
+      <c r="J49" s="5">
+        <f>-J6-I34*Inputs!$C$38</f>
+        <v>0</v>
+      </c>
+      <c r="K49" s="5">
+        <f>-K6-J34*Inputs!$C$38</f>
+        <v>0</v>
+      </c>
+      <c r="L49" s="5">
+        <f>-L6-K34*Inputs!$C$38</f>
+        <v>0</v>
+      </c>
+      <c r="M49" s="5">
+        <f>-M6-L34*Inputs!$C$38</f>
+        <v>0</v>
+      </c>
+      <c r="N49" s="5">
+        <f>-N6-M34*Inputs!$C$38</f>
+        <v>0</v>
+      </c>
+      <c r="O49" s="5">
+        <f>-O6-N34*Inputs!$C$38</f>
+        <v>0</v>
+      </c>
+      <c r="P49" s="5">
+        <f>-P6-O34*Inputs!$C$38</f>
+        <v>0</v>
+      </c>
+      <c r="Q49" s="5">
+        <f>-Q6-P34*Inputs!$C$38</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17">
+      <c r="A50" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="H50" s="5">
+        <f>H6*Inputs!$C$33-H30</f>
+        <v>0</v>
+      </c>
+      <c r="I50" s="5">
+        <f>I6*Inputs!$C$33-I30</f>
+        <v>0</v>
+      </c>
+      <c r="J50" s="5">
+        <f>J6*Inputs!$C$33-J30</f>
+        <v>0</v>
+      </c>
+      <c r="K50" s="5">
+        <f>K6*Inputs!$C$33-K30</f>
+        <v>0</v>
+      </c>
+      <c r="L50" s="5">
+        <f>L6*Inputs!$C$33-L30</f>
+        <v>0</v>
+      </c>
+      <c r="M50" s="5">
+        <f>M6*Inputs!$C$33-M30</f>
+        <v>0</v>
+      </c>
+      <c r="N50" s="5">
+        <f>N6*Inputs!$C$33-N30</f>
+        <v>0</v>
+      </c>
+      <c r="O50" s="5">
+        <f>O6*Inputs!$C$33-O30</f>
+        <v>0</v>
+      </c>
+      <c r="P50" s="5">
+        <f>P6*Inputs!$C$33-P30</f>
+        <v>0</v>
+      </c>
+      <c r="Q50" s="5">
+        <f>Q6*Inputs!$C$33-Q30</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17">
+      <c r="A51" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G51" s="5">
+        <v>0</v>
+      </c>
+      <c r="H51" s="5">
+        <f>G36+H48+H49+H50</f>
+        <v>0</v>
+      </c>
+      <c r="I51" s="5">
+        <f>H36+I48+I49+I50</f>
+        <v>0</v>
+      </c>
+      <c r="J51" s="5">
+        <f>I36+J48+J49+J50</f>
+        <v>0</v>
+      </c>
+      <c r="K51" s="5">
+        <f>J36+K48+K49+K50</f>
+        <v>0</v>
+      </c>
+      <c r="L51" s="5">
+        <f>K36+L48+L49+L50</f>
+        <v>0</v>
+      </c>
+      <c r="M51" s="5">
+        <f>L36+M48+M49+M50</f>
+        <v>0</v>
+      </c>
+      <c r="N51" s="5">
+        <f>M36+N48+N49+N50</f>
+        <v>0</v>
+      </c>
+      <c r="O51" s="5">
+        <f>N36+O48+O49+O50</f>
+        <v>0</v>
+      </c>
+      <c r="P51" s="5">
+        <f>O36+P48+P49+P50</f>
+        <v>0</v>
+      </c>
+      <c r="Q51" s="5">
+        <f>P36+Q48+Q49+Q50</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17">
+      <c r="A52" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H52" s="5">
+        <f>MAX(Inputs!$C$10-H51,-G42)</f>
+        <v>0</v>
+      </c>
+      <c r="I52" s="5">
+        <f>MAX(Inputs!$C$10-I51,-H42)</f>
+        <v>0</v>
+      </c>
+      <c r="J52" s="5">
+        <f>MAX(Inputs!$C$10-J51,-I42)</f>
+        <v>0</v>
+      </c>
+      <c r="K52" s="5">
+        <f>MAX(Inputs!$C$10-K51,-J42)</f>
+        <v>0</v>
+      </c>
+      <c r="L52" s="5">
+        <f>MAX(Inputs!$C$10-L51,-K42)</f>
+        <v>0</v>
+      </c>
+      <c r="M52" s="5">
+        <f>MAX(Inputs!$C$10-M51,-L42)</f>
+        <v>0</v>
+      </c>
+      <c r="N52" s="5">
+        <f>MAX(Inputs!$C$10-N51,-M42)</f>
+        <v>0</v>
+      </c>
+      <c r="O52" s="5">
+        <f>MAX(Inputs!$C$10-O51,-N42)</f>
+        <v>0</v>
+      </c>
+      <c r="P52" s="5">
+        <f>MAX(Inputs!$C$10-P51,-O42)</f>
+        <v>0</v>
+      </c>
+      <c r="Q52" s="5">
+        <f>MAX(Inputs!$C$10-Q51,-P42)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17">
+      <c r="A53" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C53" s="5">
+        <v>-19172</v>
+      </c>
+      <c r="D53" s="5">
+        <v>-21217</v>
+      </c>
+      <c r="E53" s="5">
+        <v>-8246</v>
+      </c>
+      <c r="F53" s="5">
+        <v>-4073</v>
+      </c>
+      <c r="G53" s="5">
+        <v>-11328</v>
+      </c>
+      <c r="H53" s="5">
+        <f>H50+H52</f>
+        <v>0</v>
+      </c>
+      <c r="I53" s="5">
+        <f>I50+I52</f>
+        <v>0</v>
+      </c>
+      <c r="J53" s="5">
+        <f>J50+J52</f>
+        <v>0</v>
+      </c>
+      <c r="K53" s="5">
+        <f>K50+K52</f>
+        <v>0</v>
+      </c>
+      <c r="L53" s="5">
+        <f>L50+L52</f>
+        <v>0</v>
+      </c>
+      <c r="M53" s="5">
+        <f>M50+M52</f>
+        <v>0</v>
+      </c>
+      <c r="N53" s="5">
+        <f>N50+N52</f>
+        <v>0</v>
+      </c>
+      <c r="O53" s="5">
+        <f>O50+O52</f>
+        <v>0</v>
+      </c>
+      <c r="P53" s="5">
+        <f>P50+P52</f>
+        <v>0</v>
+      </c>
+      <c r="Q53" s="5">
+        <f>Q50+Q52</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17">
+      <c r="A54" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="C33" s="5">
-        <v>35466</v>
-      </c>
-      <c r="D33" s="5">
-        <v>30293</v>
-      </c>
-      <c r="E33" s="5">
-        <v>34714</v>
-      </c>
-      <c r="F33" s="5">
-        <v>29904</v>
-      </c>
-      <c r="G33" s="5">
-        <v>66889</v>
-      </c>
-      <c r="H33" s="5">
-        <f>(G20+H32)*Inputs!$C$24</f>
-        <v>0</v>
-      </c>
-      <c r="I33" s="5">
-        <f>(H20+I32)*Inputs!$C$24</f>
-        <v>0</v>
-      </c>
-      <c r="J33" s="5">
-        <f>(I20+J32)*Inputs!$C$24</f>
-        <v>0</v>
-      </c>
-      <c r="K33" s="5">
-        <f>(J20+K32)*Inputs!$C$24</f>
-        <v>0</v>
-      </c>
-      <c r="L33" s="5">
-        <f>(K20+L32)*Inputs!$C$24</f>
-        <v>0</v>
-      </c>
-      <c r="M33" s="5">
-        <f>(L20+M32)*Inputs!$C$24</f>
-        <v>0</v>
-      </c>
-      <c r="N33" s="5">
-        <f>(M20+N32)*Inputs!$C$24</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14">
-      <c r="A34" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="12"/>
-      <c r="M34" s="12"/>
-      <c r="N34" s="12"/>
-    </row>
-    <row r="35" spans="1:14">
-      <c r="A35" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H35" s="5">
-        <f>(H22-H28)-(G22-G28)</f>
-        <v>0</v>
-      </c>
-      <c r="I35" s="5">
-        <f>(I22-I28)-(H22-H28)</f>
-        <v>0</v>
-      </c>
-      <c r="J35" s="5">
-        <f>(J22-J28)-(I22-I28)</f>
-        <v>0</v>
-      </c>
-      <c r="K35" s="5">
-        <f>(K22-K28)-(J22-J28)</f>
-        <v>0</v>
-      </c>
-      <c r="L35" s="5">
-        <f>(L22-L28)-(K22-K28)</f>
-        <v>0</v>
-      </c>
-      <c r="M35" s="5">
-        <f>(M22-M28)-(L22-L28)</f>
-        <v>0</v>
-      </c>
-      <c r="N35" s="5">
-        <f>(N22-N28)-(M22-M28)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14">
-      <c r="A36" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C36" s="5">
-        <v>41788</v>
-      </c>
-      <c r="D36" s="5">
-        <v>47152</v>
-      </c>
-      <c r="E36" s="5">
-        <v>40099</v>
-      </c>
-      <c r="F36" s="5">
-        <v>50488</v>
-      </c>
-      <c r="G36" s="5">
-        <v>50902</v>
-      </c>
-      <c r="H36" s="5">
-        <f>H15+H11-H35</f>
-        <v>0</v>
-      </c>
-      <c r="I36" s="5">
-        <f>I15+I11-I35</f>
-        <v>0</v>
-      </c>
-      <c r="J36" s="5">
-        <f>J15+J11-J35</f>
-        <v>0</v>
-      </c>
-      <c r="K36" s="5">
-        <f>K15+K11-K35</f>
-        <v>0</v>
-      </c>
-      <c r="L36" s="5">
-        <f>L15+L11-L35</f>
-        <v>0</v>
-      </c>
-      <c r="M36" s="5">
-        <f>M15+M11-M35</f>
-        <v>0</v>
-      </c>
-      <c r="N36" s="5">
-        <f>N15+N11-N35</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14">
-      <c r="A37" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-22891</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-26145</v>
-      </c>
-      <c r="E37" s="5">
-        <v>-31456</v>
-      </c>
-      <c r="F37" s="5">
-        <v>-45852</v>
-      </c>
-      <c r="G37" s="5">
-        <v>-37578</v>
-      </c>
-      <c r="H37" s="5">
-        <f>-H32-(H21-G21)</f>
-        <v>0</v>
-      </c>
-      <c r="I37" s="5">
-        <f>-I32-(I21-H21)</f>
-        <v>0</v>
-      </c>
-      <c r="J37" s="5">
-        <f>-J32-(J21-I21)</f>
-        <v>0</v>
-      </c>
-      <c r="K37" s="5">
-        <f>-K32-(K21-J21)</f>
-        <v>0</v>
-      </c>
-      <c r="L37" s="5">
-        <f>-L32-(L21-K21)</f>
-        <v>0</v>
-      </c>
-      <c r="M37" s="5">
-        <f>-M32-(M21-L21)</f>
-        <v>0</v>
-      </c>
-      <c r="N37" s="5">
-        <f>-N32-(N21-M21)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14">
-      <c r="A38" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-19172</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-21217</v>
-      </c>
-      <c r="E38" s="5">
-        <v>-8246</v>
-      </c>
-      <c r="F38" s="5">
-        <v>-4073</v>
-      </c>
-      <c r="G38" s="5">
-        <v>-11328</v>
-      </c>
-      <c r="H38" s="5">
-        <f>(H27-G27)-H17</f>
-        <v>0</v>
-      </c>
-      <c r="I38" s="5">
-        <f>(I27-H27)-I17</f>
-        <v>0</v>
-      </c>
-      <c r="J38" s="5">
-        <f>(J27-I27)-J17</f>
-        <v>0</v>
-      </c>
-      <c r="K38" s="5">
-        <f>(K27-J27)-K17</f>
-        <v>0</v>
-      </c>
-      <c r="L38" s="5">
-        <f>(L27-K27)-L17</f>
-        <v>0</v>
-      </c>
-      <c r="M38" s="5">
-        <f>(M27-L27)-M17</f>
-        <v>0</v>
-      </c>
-      <c r="N38" s="5">
-        <f>(N27-M27)-N17</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14">
-      <c r="A39" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="B39" s="12"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="12"/>
-      <c r="J39" s="12"/>
-      <c r="K39" s="12"/>
-      <c r="L39" s="12"/>
-      <c r="M39" s="12"/>
-      <c r="N39" s="12"/>
-    </row>
-    <row r="40" spans="1:14">
-      <c r="A40" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C40" s="11">
-        <f>C27/C9</f>
-        <v>0</v>
-      </c>
-      <c r="D40" s="11">
-        <f>D27/D9</f>
-        <v>0</v>
-      </c>
-      <c r="E40" s="11">
-        <f>E27/E9</f>
-        <v>0</v>
-      </c>
-      <c r="F40" s="11">
-        <f>F27/F9</f>
-        <v>0</v>
-      </c>
-      <c r="G40" s="11">
-        <f>G27/G9</f>
-        <v>0</v>
-      </c>
-      <c r="H40" s="11">
-        <f>(H27-H23)/H9</f>
-        <v>0</v>
-      </c>
-      <c r="I40" s="11">
-        <f>(I27-I23)/I9</f>
-        <v>0</v>
-      </c>
-      <c r="J40" s="11">
-        <f>(J27-J23)/J9</f>
-        <v>0</v>
-      </c>
-      <c r="K40" s="11">
-        <f>(K27-K23)/K9</f>
-        <v>0</v>
-      </c>
-      <c r="L40" s="11">
-        <f>(L27-L23)/L9</f>
-        <v>0</v>
-      </c>
-      <c r="M40" s="11">
-        <f>(M27-M23)/M9</f>
-        <v>0</v>
-      </c>
-      <c r="N40" s="11">
-        <f>(N27-N23)/N9</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14">
-      <c r="A41" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H41" s="6">
-        <f>H15/((H25+H26+G25+G26)/2)</f>
-        <v>0</v>
-      </c>
-      <c r="I41" s="6">
-        <f>I15/((I25+I26+H25+H26)/2)</f>
-        <v>0</v>
-      </c>
-      <c r="J41" s="6">
-        <f>J15/((J25+J26+I25+I26)/2)</f>
-        <v>0</v>
-      </c>
-      <c r="K41" s="6">
-        <f>K15/((K25+K26+J25+J26)/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L41" s="6">
-        <f>L15/((L25+L26+K25+K26)/2)</f>
-        <v>0</v>
-      </c>
-      <c r="M41" s="6">
-        <f>M15/((M25+M26+L25+L26)/2)</f>
-        <v>0</v>
-      </c>
-      <c r="N41" s="6">
-        <f>N15/((N25+N26+M25+M26)/2)</f>
+      <c r="B54" s="12"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="12"/>
+      <c r="I54" s="12"/>
+      <c r="J54" s="12"/>
+      <c r="K54" s="12"/>
+      <c r="L54" s="12"/>
+      <c r="M54" s="12"/>
+      <c r="N54" s="12"/>
+      <c r="O54" s="12"/>
+      <c r="P54" s="12"/>
+      <c r="Q54" s="12"/>
+    </row>
+    <row r="55" spans="1:17">
+      <c r="A55" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C55" s="11">
+        <f>C41/C16</f>
+        <v>0</v>
+      </c>
+      <c r="D55" s="11">
+        <f>D41/D16</f>
+        <v>0</v>
+      </c>
+      <c r="E55" s="11">
+        <f>E41/E16</f>
+        <v>0</v>
+      </c>
+      <c r="F55" s="11">
+        <f>F41/F16</f>
+        <v>0</v>
+      </c>
+      <c r="G55" s="11">
+        <f>G41/G16</f>
+        <v>0</v>
+      </c>
+      <c r="H55" s="11">
+        <f>(H41+H42-H36)/H16</f>
+        <v>0</v>
+      </c>
+      <c r="I55" s="11">
+        <f>(I41+I42-I36)/I16</f>
+        <v>0</v>
+      </c>
+      <c r="J55" s="11">
+        <f>(J41+J42-J36)/J16</f>
+        <v>0</v>
+      </c>
+      <c r="K55" s="11">
+        <f>(K41+K42-K36)/K16</f>
+        <v>0</v>
+      </c>
+      <c r="L55" s="11">
+        <f>(L41+L42-L36)/L16</f>
+        <v>0</v>
+      </c>
+      <c r="M55" s="11">
+        <f>(M41+M42-M36)/M16</f>
+        <v>0</v>
+      </c>
+      <c r="N55" s="11">
+        <f>(N41+N42-N36)/N16</f>
+        <v>0</v>
+      </c>
+      <c r="O55" s="11">
+        <f>(O41+O42-O36)/O16</f>
+        <v>0</v>
+      </c>
+      <c r="P55" s="11">
+        <f>(P41+P42-P36)/P16</f>
+        <v>0</v>
+      </c>
+      <c r="Q55" s="11">
+        <f>(Q41+Q42-Q36)/Q16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17">
+      <c r="A56" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="H56" s="6">
+        <f>H28/((H38+H39+G38+G39)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="I56" s="6">
+        <f>I28/((I38+I39+H38+H39)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="J56" s="6">
+        <f>J28/((J38+J39+I38+I39)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="K56" s="6">
+        <f>K28/((K38+K39+J38+J39)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L56" s="6">
+        <f>L28/((L38+L39+K38+K39)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="M56" s="6">
+        <f>M28/((M38+M39+L38+L39)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="N56" s="6">
+        <f>N28/((N38+N39+M38+M39)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="O56" s="6">
+        <f>O28/((O38+O39+N38+N39)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="P56" s="6">
+        <f>P28/((P38+P39+O38+O39)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="Q56" s="6">
+        <f>Q28/((Q38+Q39+P38+P39)/2)</f>
         <v>0</v>
       </c>
     </row>
@@ -3942,261 +5461,318 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="36.7109375" customWidth="1"/>
+    <col min="1" max="1" width="40.7109375" customWidth="1"/>
     <col min="2" max="2" width="8.7109375" customWidth="1"/>
     <col min="3" max="17" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="3" t="s">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="C4" s="6">
         <f>Inputs!$C$4-Inputs!$C$5</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:12">
       <c r="A5" s="2" t="s">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="C5" s="13">
-        <f>0.67*Inputs!$C$10+0.33</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <f>0.67*Inputs!$C$11+0.33</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="2" t="s">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="C6" s="6">
         <f>$C$4+$C$5*Inputs!$C$6</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:12">
       <c r="A7" s="2" t="s">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="C7" s="6">
-        <f>Inputs!$C$11*(1-Inputs!$C$7)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <f>Inputs!$C$12*(1-Inputs!$C$7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="2" t="s">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="C8" s="5">
-        <f>Model!$G$27</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <f>Model!$G$41</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" s="2" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="C9" s="5">
-        <f>Inputs!$C$14*Inputs!$C$15</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <f>Inputs!$C$15*Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" s="2" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="C10" s="6">
         <f>$C$8/($C$8+$C$9)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:12">
       <c r="A11" s="2" t="s">
-        <v>108</v>
+        <v>149</v>
       </c>
       <c r="C11" s="6">
         <f>(1-$C$10)*$C$6+$C$10*$C$7</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:12">
       <c r="A13" s="3" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>83</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="2" t="s">
-        <v>110</v>
+        <v>151</v>
       </c>
       <c r="C14" s="5">
-        <f>(Model!$H$9-Model!$H$11)*(1-Inputs!$C$7)</f>
+        <f>(Model!$H$16-Model!$H$21)*(1-Inputs!$C$7)</f>
         <v>0</v>
       </c>
       <c r="D14" s="5">
-        <f>(Model!$I$9-Model!$I$11)*(1-Inputs!$C$7)</f>
+        <f>(Model!$I$16-Model!$I$21)*(1-Inputs!$C$7)</f>
         <v>0</v>
       </c>
       <c r="E14" s="5">
-        <f>(Model!$J$9-Model!$J$11)*(1-Inputs!$C$7)</f>
+        <f>(Model!$J$16-Model!$J$21)*(1-Inputs!$C$7)</f>
         <v>0</v>
       </c>
       <c r="F14" s="5">
-        <f>(Model!$K$9-Model!$K$11)*(1-Inputs!$C$7)</f>
+        <f>(Model!$K$16-Model!$K$21)*(1-Inputs!$C$7)</f>
         <v>0</v>
       </c>
       <c r="G14" s="5">
-        <f>(Model!$L$9-Model!$L$11)*(1-Inputs!$C$7)</f>
+        <f>(Model!$L$16-Model!$L$21)*(1-Inputs!$C$7)</f>
         <v>0</v>
       </c>
       <c r="H14" s="5">
-        <f>(Model!$M$9-Model!$M$11)*(1-Inputs!$C$7)</f>
+        <f>(Model!$M$16-Model!$M$21)*(1-Inputs!$C$7)</f>
         <v>0</v>
       </c>
       <c r="I14" s="5">
-        <f>(Model!$N$9-Model!$N$11)*(1-Inputs!$C$7)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <f>(Model!$N$16-Model!$N$21)*(1-Inputs!$C$7)</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <f>(Model!$O$16-Model!$O$21)*(1-Inputs!$C$7)</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <f>(Model!$P$16-Model!$P$21)*(1-Inputs!$C$7)</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <f>(Model!$Q$16-Model!$Q$21)*(1-Inputs!$C$7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="2" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="C15" s="5">
-        <f>Model!$H$11</f>
+        <f>Model!$H$21</f>
         <v>0</v>
       </c>
       <c r="D15" s="5">
-        <f>Model!$I$11</f>
+        <f>Model!$I$21</f>
         <v>0</v>
       </c>
       <c r="E15" s="5">
-        <f>Model!$J$11</f>
+        <f>Model!$J$21</f>
         <v>0</v>
       </c>
       <c r="F15" s="5">
-        <f>Model!$K$11</f>
+        <f>Model!$K$21</f>
         <v>0</v>
       </c>
       <c r="G15" s="5">
-        <f>Model!$L$11</f>
+        <f>Model!$L$21</f>
         <v>0</v>
       </c>
       <c r="H15" s="5">
-        <f>Model!$M$11</f>
+        <f>Model!$M$21</f>
         <v>0</v>
       </c>
       <c r="I15" s="5">
-        <f>Model!$N$11</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+        <f>Model!$N$21</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <f>Model!$O$21</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <f>Model!$P$21</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <f>Model!$Q$21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C16" s="5">
-        <f>-Model!$H$32</f>
+        <f>-Model!$H$6</f>
         <v>0</v>
       </c>
       <c r="D16" s="5">
-        <f>-Model!$I$32</f>
+        <f>-Model!$I$6</f>
         <v>0</v>
       </c>
       <c r="E16" s="5">
-        <f>-Model!$J$32</f>
+        <f>-Model!$J$6</f>
         <v>0</v>
       </c>
       <c r="F16" s="5">
-        <f>-Model!$K$32</f>
+        <f>-Model!$K$6</f>
         <v>0</v>
       </c>
       <c r="G16" s="5">
-        <f>-Model!$L$32</f>
+        <f>-Model!$L$6</f>
         <v>0</v>
       </c>
       <c r="H16" s="5">
-        <f>-Model!$M$32</f>
+        <f>-Model!$M$6</f>
         <v>0</v>
       </c>
       <c r="I16" s="5">
-        <f>-Model!$N$32</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
+        <f>-Model!$N$6</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <f>-Model!$O$6</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <f>-Model!$P$6</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <f>-Model!$Q$6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" s="2" t="s">
-        <v>111</v>
+        <v>152</v>
       </c>
       <c r="C17" s="5">
-        <f>-Model!$H$35</f>
+        <f>-Model!$H$47</f>
         <v>0</v>
       </c>
       <c r="D17" s="5">
-        <f>-Model!$I$35</f>
+        <f>-Model!$I$47</f>
         <v>0</v>
       </c>
       <c r="E17" s="5">
-        <f>-Model!$J$35</f>
+        <f>-Model!$J$47</f>
         <v>0</v>
       </c>
       <c r="F17" s="5">
-        <f>-Model!$K$35</f>
+        <f>-Model!$K$47</f>
         <v>0</v>
       </c>
       <c r="G17" s="5">
-        <f>-Model!$L$35</f>
+        <f>-Model!$L$47</f>
         <v>0</v>
       </c>
       <c r="H17" s="5">
-        <f>-Model!$M$35</f>
+        <f>-Model!$M$47</f>
         <v>0</v>
       </c>
       <c r="I17" s="5">
-        <f>-Model!$N$35</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
+        <f>-Model!$N$47</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <f>-Model!$O$47</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <f>-Model!$P$47</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <f>-Model!$Q$47</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" s="2" t="s">
-        <v>112</v>
+        <v>153</v>
       </c>
       <c r="C18" s="14">
         <f>SUM(C14:C17)</f>
@@ -4226,10 +5802,22 @@
         <f>SUM(I14:I17)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="J18" s="14">
+        <f>SUM(J14:J17)</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="14">
+        <f>SUM(K14:K17)</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="14">
+        <f>SUM(L14:L17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" s="2" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="C19" s="5">
         <f>C18*Inputs!$C$8</f>
@@ -4259,10 +5847,22 @@
         <f>I18*1</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:9">
+      <c r="J19" s="5">
+        <f>J18*1</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="5">
+        <f>K18*1</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="5">
+        <f>L18*1</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" s="2" t="s">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="C20" s="13">
         <f>Inputs!$C$8+0</f>
@@ -4292,10 +5892,22 @@
         <f>Inputs!$C$8+6</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="J20" s="13">
+        <f>Inputs!$C$8+7</f>
+        <v>0</v>
+      </c>
+      <c r="K20" s="13">
+        <f>Inputs!$C$8+8</f>
+        <v>0</v>
+      </c>
+      <c r="L20" s="13">
+        <f>Inputs!$C$8+9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" s="2" t="s">
-        <v>115</v>
+        <v>156</v>
       </c>
       <c r="C21" s="13">
         <f>1/(1+DCF!$C$11)^C20</f>
@@ -4325,10 +5937,22 @@
         <f>1/(1+DCF!$C$11)^I20</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:9">
+      <c r="J21" s="13">
+        <f>1/(1+DCF!$C$11)^J20</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="13">
+        <f>1/(1+DCF!$C$11)^K20</f>
+        <v>0</v>
+      </c>
+      <c r="L21" s="13">
+        <f>1/(1+DCF!$C$11)^L20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" s="2" t="s">
-        <v>116</v>
+        <v>157</v>
       </c>
       <c r="C22" s="5">
         <f>C19*C21</f>
@@ -4358,82 +5982,94 @@
         <f>I19*I21</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:9">
+      <c r="J22" s="5">
+        <f>J19*J21</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="5">
+        <f>K19*K21</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="5">
+        <f>L19*L21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25" s="2" t="s">
-        <v>117</v>
+        <v>158</v>
       </c>
       <c r="C25" s="5">
-        <f>SUM(C22:I22)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
+        <f>SUM(C22:L22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26" s="2" t="s">
-        <v>118</v>
+        <v>159</v>
       </c>
       <c r="C26" s="5">
-        <f>I14*(1+Inputs!$C$12)*(1-Inputs!$C$12/Inputs!$C$13)/(DCF!$C$11-Inputs!$C$12)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+        <f>L14*(1+Inputs!$C$13)*(1-Inputs!$C$13/Inputs!$C$14)/(DCF!$C$11-Inputs!$C$13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27" s="2" t="s">
-        <v>119</v>
+        <v>160</v>
       </c>
       <c r="C27" s="5">
-        <f>$C$26/(1+DCF!$C$11)^I20</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
+        <f>$C$26/(1+DCF!$C$11)^L20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
       <c r="A28" s="2" t="s">
-        <v>120</v>
+        <v>161</v>
       </c>
       <c r="C28" s="14">
         <f>$C$25+$C$27</f>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:12">
       <c r="A29" s="2" t="s">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="C29" s="5">
-        <f>-Model!$G$27</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
+        <f>-Model!$G$41</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
       <c r="A30" s="2" t="s">
-        <v>122</v>
+        <v>163</v>
       </c>
       <c r="C30" s="5">
-        <f>Inputs!$C$16</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
+        <f>Inputs!$C$17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31" s="2" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="C31" s="5">
-        <f>Model!$G$21</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
+        <f>Model!$G$34</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32" s="2" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
       <c r="C32" s="5">
-        <f>-Inputs!$C$17</f>
+        <f>-Inputs!$C$18</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
       <c r="C33" s="14">
         <f>SUM($C$28,$C$29,$C$30,$C$31,$C$32)</f>
@@ -4442,16 +6078,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2" t="s">
-        <v>126</v>
+        <v>167</v>
       </c>
       <c r="C34" s="4">
-        <f>$C$33/Inputs!$C$15</f>
+        <f>$C$33/Inputs!$C$16</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2" t="s">
-        <v>127</v>
+        <v>168</v>
       </c>
       <c r="C35" s="6">
         <f>$C$27/$C$28</f>
@@ -4460,198 +6096,216 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
       <c r="C36" s="5">
-        <f>Inputs!$C$18*Model!$G$9</f>
+        <f>$C$34*(1+DCF!$C$6)-Model!$H$30/Inputs!$C$16</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C37" s="4">
-        <f>($C$36-Model!$G$27+Inputs!$C$16-Inputs!$C$17)/Inputs!$C$15</f>
+        <v>170</v>
+      </c>
+      <c r="C37" s="5">
+        <f>Inputs!$C$19*Model!$H$16</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C38" s="4">
-        <f>Inputs!$C$9*$C$34+(1-Inputs!$C$9)*$C$37</f>
+        <v>171</v>
+      </c>
+      <c r="C38" s="5">
+        <f>($C$37-Model!$H$41-Model!$H$42+Inputs!$C$17+Model!$H$36-Model!$H$40)/Inputs!$C$16</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C39" s="6">
-        <f>$C$38/Inputs!$C$14-1</f>
+        <v>172</v>
+      </c>
+      <c r="C39" s="5">
+        <f>SOTP!$C$30</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C40" s="3">
-        <f>IF($C$39&gt;0.15,"BUY",IF($C$39&lt;-0.1,"SELL","HOLD"))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="C44" s="8">
+        <v>173</v>
+      </c>
+      <c r="C40" s="4">
+        <f>$C$39</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C41" s="6">
+        <f>$C$40/Inputs!$C$15-1</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C42" s="3">
+        <f>IF($C$41&gt;0.15,"BUY",IF($C$41&lt;-0.1,"SELL","HOLD"))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="C46" s="8">
         <v>0.04</v>
       </c>
-      <c r="D44" s="8">
+      <c r="D46" s="8">
         <v>0.045</v>
       </c>
-      <c r="E44" s="8">
+      <c r="E46" s="8">
         <v>0.05</v>
       </c>
-      <c r="F44" s="8">
+      <c r="F46" s="8">
         <v>0.055</v>
       </c>
-      <c r="G44" s="8">
+      <c r="G46" s="8">
         <v>0.06</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="B45" s="6">
-        <f>DCF!$C$11+-0.01</f>
-        <v>0</v>
-      </c>
-      <c r="C45" s="5">
-        <f>(SUMPRODUCT($C$19:$I$19/(1+$B45)^$C$20:$I$20)+$I$14*(1+C$44)*(1-C$44/Inputs!$C$13)/($B45-C$44)/(1+$B45)^$I$20-Model!$G$27+Inputs!$C$16+Model!$G$21-Inputs!$C$17)/Inputs!$C$15</f>
-        <v>0</v>
-      </c>
-      <c r="D45" s="5">
-        <f>(SUMPRODUCT($C$19:$I$19/(1+$B45)^$C$20:$I$20)+$I$14*(1+D$44)*(1-D$44/Inputs!$C$13)/($B45-D$44)/(1+$B45)^$I$20-Model!$G$27+Inputs!$C$16+Model!$G$21-Inputs!$C$17)/Inputs!$C$15</f>
-        <v>0</v>
-      </c>
-      <c r="E45" s="5">
-        <f>(SUMPRODUCT($C$19:$I$19/(1+$B45)^$C$20:$I$20)+$I$14*(1+E$44)*(1-E$44/Inputs!$C$13)/($B45-E$44)/(1+$B45)^$I$20-Model!$G$27+Inputs!$C$16+Model!$G$21-Inputs!$C$17)/Inputs!$C$15</f>
-        <v>0</v>
-      </c>
-      <c r="F45" s="5">
-        <f>(SUMPRODUCT($C$19:$I$19/(1+$B45)^$C$20:$I$20)+$I$14*(1+F$44)*(1-F$44/Inputs!$C$13)/($B45-F$44)/(1+$B45)^$I$20-Model!$G$27+Inputs!$C$16+Model!$G$21-Inputs!$C$17)/Inputs!$C$15</f>
-        <v>0</v>
-      </c>
-      <c r="G45" s="5">
-        <f>(SUMPRODUCT($C$19:$I$19/(1+$B45)^$C$20:$I$20)+$I$14*(1+G$44)*(1-G$44/Inputs!$C$13)/($B45-G$44)/(1+$B45)^$I$20-Model!$G$27+Inputs!$C$16+Model!$G$21-Inputs!$C$17)/Inputs!$C$15</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="B46" s="6">
-        <f>DCF!$C$11+-0.005</f>
-        <v>0</v>
-      </c>
-      <c r="C46" s="5">
-        <f>(SUMPRODUCT($C$19:$I$19/(1+$B46)^$C$20:$I$20)+$I$14*(1+C$44)*(1-C$44/Inputs!$C$13)/($B46-C$44)/(1+$B46)^$I$20-Model!$G$27+Inputs!$C$16+Model!$G$21-Inputs!$C$17)/Inputs!$C$15</f>
-        <v>0</v>
-      </c>
-      <c r="D46" s="5">
-        <f>(SUMPRODUCT($C$19:$I$19/(1+$B46)^$C$20:$I$20)+$I$14*(1+D$44)*(1-D$44/Inputs!$C$13)/($B46-D$44)/(1+$B46)^$I$20-Model!$G$27+Inputs!$C$16+Model!$G$21-Inputs!$C$17)/Inputs!$C$15</f>
-        <v>0</v>
-      </c>
-      <c r="E46" s="5">
-        <f>(SUMPRODUCT($C$19:$I$19/(1+$B46)^$C$20:$I$20)+$I$14*(1+E$44)*(1-E$44/Inputs!$C$13)/($B46-E$44)/(1+$B46)^$I$20-Model!$G$27+Inputs!$C$16+Model!$G$21-Inputs!$C$17)/Inputs!$C$15</f>
-        <v>0</v>
-      </c>
-      <c r="F46" s="5">
-        <f>(SUMPRODUCT($C$19:$I$19/(1+$B46)^$C$20:$I$20)+$I$14*(1+F$44)*(1-F$44/Inputs!$C$13)/($B46-F$44)/(1+$B46)^$I$20-Model!$G$27+Inputs!$C$16+Model!$G$21-Inputs!$C$17)/Inputs!$C$15</f>
-        <v>0</v>
-      </c>
-      <c r="G46" s="5">
-        <f>(SUMPRODUCT($C$19:$I$19/(1+$B46)^$C$20:$I$20)+$I$14*(1+G$44)*(1-G$44/Inputs!$C$13)/($B46-G$44)/(1+$B46)^$I$20-Model!$G$27+Inputs!$C$16+Model!$G$21-Inputs!$C$17)/Inputs!$C$15</f>
-        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="B47" s="6">
-        <f>DCF!$C$11+0</f>
+        <f>DCF!$C$11+-0.01</f>
         <v>0</v>
       </c>
       <c r="C47" s="5">
-        <f>(SUMPRODUCT($C$19:$I$19/(1+$B47)^$C$20:$I$20)+$I$14*(1+C$44)*(1-C$44/Inputs!$C$13)/($B47-C$44)/(1+$B47)^$I$20-Model!$G$27+Inputs!$C$16+Model!$G$21-Inputs!$C$17)/Inputs!$C$15</f>
+        <f>(SUMPRODUCT($C$19:$L$19/(1+$B47)^$C$20:$L$20)+$L$14*(1+C$46)*(1-C$46/Inputs!$C$14)/($B47-C$46)/(1+$B47)^$L$20-Model!$G$41+Inputs!$C$17+Model!$G$34-Inputs!$C$18)/Inputs!$C$16</f>
         <v>0</v>
       </c>
       <c r="D47" s="5">
-        <f>(SUMPRODUCT($C$19:$I$19/(1+$B47)^$C$20:$I$20)+$I$14*(1+D$44)*(1-D$44/Inputs!$C$13)/($B47-D$44)/(1+$B47)^$I$20-Model!$G$27+Inputs!$C$16+Model!$G$21-Inputs!$C$17)/Inputs!$C$15</f>
+        <f>(SUMPRODUCT($C$19:$L$19/(1+$B47)^$C$20:$L$20)+$L$14*(1+D$46)*(1-D$46/Inputs!$C$14)/($B47-D$46)/(1+$B47)^$L$20-Model!$G$41+Inputs!$C$17+Model!$G$34-Inputs!$C$18)/Inputs!$C$16</f>
         <v>0</v>
       </c>
       <c r="E47" s="5">
-        <f>(SUMPRODUCT($C$19:$I$19/(1+$B47)^$C$20:$I$20)+$I$14*(1+E$44)*(1-E$44/Inputs!$C$13)/($B47-E$44)/(1+$B47)^$I$20-Model!$G$27+Inputs!$C$16+Model!$G$21-Inputs!$C$17)/Inputs!$C$15</f>
+        <f>(SUMPRODUCT($C$19:$L$19/(1+$B47)^$C$20:$L$20)+$L$14*(1+E$46)*(1-E$46/Inputs!$C$14)/($B47-E$46)/(1+$B47)^$L$20-Model!$G$41+Inputs!$C$17+Model!$G$34-Inputs!$C$18)/Inputs!$C$16</f>
         <v>0</v>
       </c>
       <c r="F47" s="5">
-        <f>(SUMPRODUCT($C$19:$I$19/(1+$B47)^$C$20:$I$20)+$I$14*(1+F$44)*(1-F$44/Inputs!$C$13)/($B47-F$44)/(1+$B47)^$I$20-Model!$G$27+Inputs!$C$16+Model!$G$21-Inputs!$C$17)/Inputs!$C$15</f>
+        <f>(SUMPRODUCT($C$19:$L$19/(1+$B47)^$C$20:$L$20)+$L$14*(1+F$46)*(1-F$46/Inputs!$C$14)/($B47-F$46)/(1+$B47)^$L$20-Model!$G$41+Inputs!$C$17+Model!$G$34-Inputs!$C$18)/Inputs!$C$16</f>
         <v>0</v>
       </c>
       <c r="G47" s="5">
-        <f>(SUMPRODUCT($C$19:$I$19/(1+$B47)^$C$20:$I$20)+$I$14*(1+G$44)*(1-G$44/Inputs!$C$13)/($B47-G$44)/(1+$B47)^$I$20-Model!$G$27+Inputs!$C$16+Model!$G$21-Inputs!$C$17)/Inputs!$C$15</f>
+        <f>(SUMPRODUCT($C$19:$L$19/(1+$B47)^$C$20:$L$20)+$L$14*(1+G$46)*(1-G$46/Inputs!$C$14)/($B47-G$46)/(1+$B47)^$L$20-Model!$G$41+Inputs!$C$17+Model!$G$34-Inputs!$C$18)/Inputs!$C$16</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="B48" s="6">
-        <f>DCF!$C$11+0.005</f>
+        <f>DCF!$C$11+-0.005</f>
         <v>0</v>
       </c>
       <c r="C48" s="5">
-        <f>(SUMPRODUCT($C$19:$I$19/(1+$B48)^$C$20:$I$20)+$I$14*(1+C$44)*(1-C$44/Inputs!$C$13)/($B48-C$44)/(1+$B48)^$I$20-Model!$G$27+Inputs!$C$16+Model!$G$21-Inputs!$C$17)/Inputs!$C$15</f>
+        <f>(SUMPRODUCT($C$19:$L$19/(1+$B48)^$C$20:$L$20)+$L$14*(1+C$46)*(1-C$46/Inputs!$C$14)/($B48-C$46)/(1+$B48)^$L$20-Model!$G$41+Inputs!$C$17+Model!$G$34-Inputs!$C$18)/Inputs!$C$16</f>
         <v>0</v>
       </c>
       <c r="D48" s="5">
-        <f>(SUMPRODUCT($C$19:$I$19/(1+$B48)^$C$20:$I$20)+$I$14*(1+D$44)*(1-D$44/Inputs!$C$13)/($B48-D$44)/(1+$B48)^$I$20-Model!$G$27+Inputs!$C$16+Model!$G$21-Inputs!$C$17)/Inputs!$C$15</f>
+        <f>(SUMPRODUCT($C$19:$L$19/(1+$B48)^$C$20:$L$20)+$L$14*(1+D$46)*(1-D$46/Inputs!$C$14)/($B48-D$46)/(1+$B48)^$L$20-Model!$G$41+Inputs!$C$17+Model!$G$34-Inputs!$C$18)/Inputs!$C$16</f>
         <v>0</v>
       </c>
       <c r="E48" s="5">
-        <f>(SUMPRODUCT($C$19:$I$19/(1+$B48)^$C$20:$I$20)+$I$14*(1+E$44)*(1-E$44/Inputs!$C$13)/($B48-E$44)/(1+$B48)^$I$20-Model!$G$27+Inputs!$C$16+Model!$G$21-Inputs!$C$17)/Inputs!$C$15</f>
+        <f>(SUMPRODUCT($C$19:$L$19/(1+$B48)^$C$20:$L$20)+$L$14*(1+E$46)*(1-E$46/Inputs!$C$14)/($B48-E$46)/(1+$B48)^$L$20-Model!$G$41+Inputs!$C$17+Model!$G$34-Inputs!$C$18)/Inputs!$C$16</f>
         <v>0</v>
       </c>
       <c r="F48" s="5">
-        <f>(SUMPRODUCT($C$19:$I$19/(1+$B48)^$C$20:$I$20)+$I$14*(1+F$44)*(1-F$44/Inputs!$C$13)/($B48-F$44)/(1+$B48)^$I$20-Model!$G$27+Inputs!$C$16+Model!$G$21-Inputs!$C$17)/Inputs!$C$15</f>
+        <f>(SUMPRODUCT($C$19:$L$19/(1+$B48)^$C$20:$L$20)+$L$14*(1+F$46)*(1-F$46/Inputs!$C$14)/($B48-F$46)/(1+$B48)^$L$20-Model!$G$41+Inputs!$C$17+Model!$G$34-Inputs!$C$18)/Inputs!$C$16</f>
         <v>0</v>
       </c>
       <c r="G48" s="5">
-        <f>(SUMPRODUCT($C$19:$I$19/(1+$B48)^$C$20:$I$20)+$I$14*(1+G$44)*(1-G$44/Inputs!$C$13)/($B48-G$44)/(1+$B48)^$I$20-Model!$G$27+Inputs!$C$16+Model!$G$21-Inputs!$C$17)/Inputs!$C$15</f>
+        <f>(SUMPRODUCT($C$19:$L$19/(1+$B48)^$C$20:$L$20)+$L$14*(1+G$46)*(1-G$46/Inputs!$C$14)/($B48-G$46)/(1+$B48)^$L$20-Model!$G$41+Inputs!$C$17+Model!$G$34-Inputs!$C$18)/Inputs!$C$16</f>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="2:7">
       <c r="B49" s="6">
+        <f>DCF!$C$11+0</f>
+        <v>0</v>
+      </c>
+      <c r="C49" s="5">
+        <f>(SUMPRODUCT($C$19:$L$19/(1+$B49)^$C$20:$L$20)+$L$14*(1+C$46)*(1-C$46/Inputs!$C$14)/($B49-C$46)/(1+$B49)^$L$20-Model!$G$41+Inputs!$C$17+Model!$G$34-Inputs!$C$18)/Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+      <c r="D49" s="5">
+        <f>(SUMPRODUCT($C$19:$L$19/(1+$B49)^$C$20:$L$20)+$L$14*(1+D$46)*(1-D$46/Inputs!$C$14)/($B49-D$46)/(1+$B49)^$L$20-Model!$G$41+Inputs!$C$17+Model!$G$34-Inputs!$C$18)/Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+      <c r="E49" s="5">
+        <f>(SUMPRODUCT($C$19:$L$19/(1+$B49)^$C$20:$L$20)+$L$14*(1+E$46)*(1-E$46/Inputs!$C$14)/($B49-E$46)/(1+$B49)^$L$20-Model!$G$41+Inputs!$C$17+Model!$G$34-Inputs!$C$18)/Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+      <c r="F49" s="5">
+        <f>(SUMPRODUCT($C$19:$L$19/(1+$B49)^$C$20:$L$20)+$L$14*(1+F$46)*(1-F$46/Inputs!$C$14)/($B49-F$46)/(1+$B49)^$L$20-Model!$G$41+Inputs!$C$17+Model!$G$34-Inputs!$C$18)/Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+      <c r="G49" s="5">
+        <f>(SUMPRODUCT($C$19:$L$19/(1+$B49)^$C$20:$L$20)+$L$14*(1+G$46)*(1-G$46/Inputs!$C$14)/($B49-G$46)/(1+$B49)^$L$20-Model!$G$41+Inputs!$C$17+Model!$G$34-Inputs!$C$18)/Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7">
+      <c r="B50" s="6">
+        <f>DCF!$C$11+0.005</f>
+        <v>0</v>
+      </c>
+      <c r="C50" s="5">
+        <f>(SUMPRODUCT($C$19:$L$19/(1+$B50)^$C$20:$L$20)+$L$14*(1+C$46)*(1-C$46/Inputs!$C$14)/($B50-C$46)/(1+$B50)^$L$20-Model!$G$41+Inputs!$C$17+Model!$G$34-Inputs!$C$18)/Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+      <c r="D50" s="5">
+        <f>(SUMPRODUCT($C$19:$L$19/(1+$B50)^$C$20:$L$20)+$L$14*(1+D$46)*(1-D$46/Inputs!$C$14)/($B50-D$46)/(1+$B50)^$L$20-Model!$G$41+Inputs!$C$17+Model!$G$34-Inputs!$C$18)/Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+      <c r="E50" s="5">
+        <f>(SUMPRODUCT($C$19:$L$19/(1+$B50)^$C$20:$L$20)+$L$14*(1+E$46)*(1-E$46/Inputs!$C$14)/($B50-E$46)/(1+$B50)^$L$20-Model!$G$41+Inputs!$C$17+Model!$G$34-Inputs!$C$18)/Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+      <c r="F50" s="5">
+        <f>(SUMPRODUCT($C$19:$L$19/(1+$B50)^$C$20:$L$20)+$L$14*(1+F$46)*(1-F$46/Inputs!$C$14)/($B50-F$46)/(1+$B50)^$L$20-Model!$G$41+Inputs!$C$17+Model!$G$34-Inputs!$C$18)/Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+      <c r="G50" s="5">
+        <f>(SUMPRODUCT($C$19:$L$19/(1+$B50)^$C$20:$L$20)+$L$14*(1+G$46)*(1-G$46/Inputs!$C$14)/($B50-G$46)/(1+$B50)^$L$20-Model!$G$41+Inputs!$C$17+Model!$G$34-Inputs!$C$18)/Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7">
+      <c r="B51" s="6">
         <f>DCF!$C$11+0.01</f>
         <v>0</v>
       </c>
-      <c r="C49" s="5">
-        <f>(SUMPRODUCT($C$19:$I$19/(1+$B49)^$C$20:$I$20)+$I$14*(1+C$44)*(1-C$44/Inputs!$C$13)/($B49-C$44)/(1+$B49)^$I$20-Model!$G$27+Inputs!$C$16+Model!$G$21-Inputs!$C$17)/Inputs!$C$15</f>
-        <v>0</v>
-      </c>
-      <c r="D49" s="5">
-        <f>(SUMPRODUCT($C$19:$I$19/(1+$B49)^$C$20:$I$20)+$I$14*(1+D$44)*(1-D$44/Inputs!$C$13)/($B49-D$44)/(1+$B49)^$I$20-Model!$G$27+Inputs!$C$16+Model!$G$21-Inputs!$C$17)/Inputs!$C$15</f>
-        <v>0</v>
-      </c>
-      <c r="E49" s="5">
-        <f>(SUMPRODUCT($C$19:$I$19/(1+$B49)^$C$20:$I$20)+$I$14*(1+E$44)*(1-E$44/Inputs!$C$13)/($B49-E$44)/(1+$B49)^$I$20-Model!$G$27+Inputs!$C$16+Model!$G$21-Inputs!$C$17)/Inputs!$C$15</f>
-        <v>0</v>
-      </c>
-      <c r="F49" s="5">
-        <f>(SUMPRODUCT($C$19:$I$19/(1+$B49)^$C$20:$I$20)+$I$14*(1+F$44)*(1-F$44/Inputs!$C$13)/($B49-F$44)/(1+$B49)^$I$20-Model!$G$27+Inputs!$C$16+Model!$G$21-Inputs!$C$17)/Inputs!$C$15</f>
-        <v>0</v>
-      </c>
-      <c r="G49" s="5">
-        <f>(SUMPRODUCT($C$19:$I$19/(1+$B49)^$C$20:$I$20)+$I$14*(1+G$44)*(1-G$44/Inputs!$C$13)/($B49-G$44)/(1+$B49)^$I$20-Model!$G$27+Inputs!$C$16+Model!$G$21-Inputs!$C$17)/Inputs!$C$15</f>
+      <c r="C51" s="5">
+        <f>(SUMPRODUCT($C$19:$L$19/(1+$B51)^$C$20:$L$20)+$L$14*(1+C$46)*(1-C$46/Inputs!$C$14)/($B51-C$46)/(1+$B51)^$L$20-Model!$G$41+Inputs!$C$17+Model!$G$34-Inputs!$C$18)/Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+      <c r="D51" s="5">
+        <f>(SUMPRODUCT($C$19:$L$19/(1+$B51)^$C$20:$L$20)+$L$14*(1+D$46)*(1-D$46/Inputs!$C$14)/($B51-D$46)/(1+$B51)^$L$20-Model!$G$41+Inputs!$C$17+Model!$G$34-Inputs!$C$18)/Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+      <c r="E51" s="5">
+        <f>(SUMPRODUCT($C$19:$L$19/(1+$B51)^$C$20:$L$20)+$L$14*(1+E$46)*(1-E$46/Inputs!$C$14)/($B51-E$46)/(1+$B51)^$L$20-Model!$G$41+Inputs!$C$17+Model!$G$34-Inputs!$C$18)/Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+      <c r="F51" s="5">
+        <f>(SUMPRODUCT($C$19:$L$19/(1+$B51)^$C$20:$L$20)+$L$14*(1+F$46)*(1-F$46/Inputs!$C$14)/($B51-F$46)/(1+$B51)^$L$20-Model!$G$41+Inputs!$C$17+Model!$G$34-Inputs!$C$18)/Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+      <c r="G51" s="5">
+        <f>(SUMPRODUCT($C$19:$L$19/(1+$B51)^$C$20:$L$20)+$L$14*(1+G$46)*(1-G$46/Inputs!$C$14)/($B51-G$46)/(1+$B51)^$L$20-Model!$G$41+Inputs!$C$17+Model!$G$34-Inputs!$C$18)/Inputs!$C$16</f>
         <v>0</v>
       </c>
     </row>
@@ -4661,6 +6315,321 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="46.7109375" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" customWidth="1"/>
+    <col min="3" max="17" width="11.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="5">
+        <f>Model!$H$14</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <f>Model!$I$14</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <f>Model!$J$14</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <f>Model!$K$14</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <f>Model!$L$14</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <f>Model!$M$14</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <f>Model!$N$14</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <f>Model!$O$14</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <f>Model!$P$14</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <f>Model!$Q$14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D6" s="5">
+        <f>(Inputs!$C$42-DCF!$C$6)*C5</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <f>(Inputs!$C$42-DCF!$C$6)*D5</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <f>(Inputs!$C$42-DCF!$C$6)*E5</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <f>(Inputs!$C$42-DCF!$C$6)*F5</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <f>(Inputs!$C$42-DCF!$C$6)*G5</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <f>(Inputs!$C$42-DCF!$C$6)*H5</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <f>(Inputs!$C$42-DCF!$C$6)*I5</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <f>(Inputs!$C$42-DCF!$C$6)*J5</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <f>(Inputs!$C$42-DCF!$C$6)*K5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D7" s="13">
+        <f>1/(1+DCF!$C$6)^1</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="13">
+        <f>1/(1+DCF!$C$6)^2</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="13">
+        <f>1/(1+DCF!$C$6)^3</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="13">
+        <f>1/(1+DCF!$C$6)^4</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="13">
+        <f>1/(1+DCF!$C$6)^5</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="13">
+        <f>1/(1+DCF!$C$6)^6</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="13">
+        <f>1/(1+DCF!$C$6)^7</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="13">
+        <f>1/(1+DCF!$C$6)^8</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="13">
+        <f>1/(1+DCF!$C$6)^9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D8" s="5">
+        <f>D6*D7</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <f>E6*E7</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <f>F6*F7</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <f>G6*G7</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <f>H6*H7</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <f>I6*I7</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <f>J6*J7</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <f>K6*K7</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <f>L6*L7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C11" s="5">
+        <f>$C$5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C12" s="5">
+        <f>SUM(D8:L8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C13" s="5">
+        <f>(Inputs!$C$42-DCF!$C$6)*L5/(DCF!$C$6-Inputs!$C$43)/(1+DCF!$C$6)^9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C14" s="5">
+        <f>SUM(C11:C13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C15" s="11">
+        <f>C14/C11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C16" s="5">
+        <f>Inputs!$C$41*(1-Inputs!$C$21)*Model!$H$33</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C17" s="5">
+        <f>Inputs!$C$45*Inputs!$C$44*(1-Inputs!$C$46)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C29" s="14">
+        <f>C14+C16+C17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C30" s="4">
+        <f>C29/Inputs!$C$16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="7" t="s">
+        <v>192</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4671,47 +6640,47 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>141</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="3" t="s">
-        <v>142</v>
+        <v>204</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>144</v>
+        <v>206</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>145</v>
+        <v>207</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>146</v>
+        <v>208</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>147</v>
+        <v>209</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>148</v>
+        <v>210</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>149</v>
+        <v>211</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>150</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>151</v>
+        <v>213</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>152</v>
+        <v>214</v>
       </c>
       <c r="C4" s="5">
         <v>390997.185143875</v>
@@ -4740,10 +6709,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>134</v>
+        <v>193</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>153</v>
+        <v>215</v>
       </c>
       <c r="C5" s="5">
         <v>316693.11593644</v>
@@ -4772,10 +6741,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>154</v>
+        <v>216</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>155</v>
+        <v>217</v>
       </c>
       <c r="C6" s="5">
         <v>250651.27292205</v>
@@ -4804,10 +6773,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>156</v>
+        <v>218</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>157</v>
+        <v>219</v>
       </c>
       <c r="C7" s="5">
         <v>213572.8602573</v>
@@ -4836,10 +6805,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>158</v>
+        <v>220</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>159</v>
+        <v>221</v>
       </c>
       <c r="C8" s="5">
         <v>117428.72835225</v>
@@ -4868,10 +6837,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>160</v>
+        <v>222</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>161</v>
+        <v>223</v>
       </c>
       <c r="C9" s="5">
         <v>92818.85147831999</v>
@@ -4900,10 +6869,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>162</v>
+        <v>224</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>163</v>
+        <v>225</v>
       </c>
       <c r="C10" s="5">
         <v>76342.264518</v>
@@ -4932,10 +6901,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>164</v>
+        <v>226</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>159</v>
+        <v>221</v>
       </c>
       <c r="C11" s="5">
         <v>63219.73850477999</v>
@@ -4964,10 +6933,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>165</v>
+        <v>227</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>166</v>
+        <v>228</v>
       </c>
       <c r="C12" s="5">
         <v>36406.144169295</v>
@@ -4996,10 +6965,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>167</v>
+        <v>229</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>163</v>
+        <v>225</v>
       </c>
       <c r="C13" s="5">
         <v>24270.4150008</v>
@@ -5028,10 +6997,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>168</v>
+        <v>230</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>159</v>
+        <v>221</v>
       </c>
       <c r="C14" s="5">
         <v>18539.42803398</v>
@@ -5060,10 +7029,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>169</v>
+        <v>231</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>152</v>
+        <v>214</v>
       </c>
       <c r="C15" s="5">
         <v>10876.439158449</v>
@@ -5092,10 +7061,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>170</v>
+        <v>232</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>152</v>
+        <v>214</v>
       </c>
       <c r="C16" s="5">
         <v>8507.280877061999</v>
@@ -5121,10 +7090,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>171</v>
+        <v>233</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>172</v>
+        <v>234</v>
       </c>
       <c r="C17" s="5">
         <v>4590.793050389</v>
@@ -5156,7 +7125,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D153"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5170,2121 +7139,2121 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>174</v>
+        <v>236</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>175</v>
+        <v>237</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>176</v>
+        <v>238</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>177</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B4" s="16">
         <v>5</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>179</v>
+        <v>241</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>180</v>
+        <v>242</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B5" s="16">
         <v>10</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>181</v>
+        <v>243</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>182</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B6" s="16">
         <v>10</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>183</v>
+        <v>245</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>184</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B7" s="16">
         <v>10</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>185</v>
+        <v>247</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>186</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B8" s="16">
         <v>10</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>187</v>
+        <v>249</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>188</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B9" s="16">
         <v>10</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>189</v>
+        <v>251</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>190</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B10" s="16">
         <v>10</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>191</v>
+        <v>253</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>192</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B11" s="16">
         <v>10</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>193</v>
+        <v>255</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>194</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B12" s="16">
         <v>10</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>195</v>
+        <v>257</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>196</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B13" s="16">
         <v>11</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>197</v>
+        <v>259</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>198</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B14" s="16">
         <v>11</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>199</v>
+        <v>261</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>200</v>
+        <v>262</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B15" s="16">
         <v>14</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>201</v>
+        <v>263</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>202</v>
+        <v>264</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B16" s="16">
         <v>15</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>203</v>
+        <v>265</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>204</v>
+        <v>266</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B17" s="16">
         <v>15</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>205</v>
+        <v>267</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>206</v>
+        <v>268</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B18" s="16">
         <v>16</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>207</v>
+        <v>269</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>208</v>
+        <v>270</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B19" s="16">
         <v>16</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>209</v>
+        <v>271</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>210</v>
+        <v>272</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B20" s="16">
         <v>17</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>195</v>
+        <v>257</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>211</v>
+        <v>273</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B21" s="16">
         <v>19</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>212</v>
+        <v>274</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>213</v>
+        <v>275</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B22" s="16">
         <v>19</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>214</v>
+        <v>276</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>215</v>
+        <v>277</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B23" s="16">
         <v>21</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>216</v>
+        <v>278</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>217</v>
+        <v>279</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B24" s="16">
         <v>21</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>218</v>
+        <v>280</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>219</v>
+        <v>281</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B25" s="16">
         <v>21</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>220</v>
+        <v>282</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>221</v>
+        <v>283</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B26" s="16">
         <v>21</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>222</v>
+        <v>284</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>223</v>
+        <v>285</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B27" s="16">
         <v>23</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>209</v>
+        <v>271</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>224</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B28" s="16">
         <v>23</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>209</v>
+        <v>271</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>225</v>
+        <v>287</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B29" s="16">
         <v>24</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>226</v>
+        <v>288</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>227</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B30" s="16">
         <v>5</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>228</v>
+        <v>290</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>229</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B31" s="16">
         <v>10</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>230</v>
+        <v>292</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>231</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B32" s="16">
         <v>22</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>228</v>
+        <v>290</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>232</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B33" s="16">
         <v>10</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>234</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B34" s="16">
         <v>7</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>235</v>
+        <v>297</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>236</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B35" s="16">
         <v>10</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>237</v>
+        <v>299</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>238</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B36" s="16">
         <v>5</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>239</v>
+        <v>301</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>240</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B37" s="16">
         <v>5</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>241</v>
+        <v>303</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>242</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B38" s="16">
         <v>6</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>243</v>
+        <v>305</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>244</v>
+        <v>306</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B39" s="16">
         <v>5</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>245</v>
+        <v>307</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>246</v>
+        <v>308</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B40" s="16">
         <v>6</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>247</v>
+        <v>309</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>248</v>
+        <v>310</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B41" s="16">
         <v>6</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>228</v>
+        <v>290</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>249</v>
+        <v>311</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B42" s="16">
         <v>6</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>250</v>
+        <v>312</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>251</v>
+        <v>313</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B43" s="16">
         <v>7</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>252</v>
+        <v>314</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>253</v>
+        <v>315</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B44" s="16">
         <v>7</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>254</v>
+        <v>316</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>255</v>
+        <v>317</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B45" s="16">
         <v>7</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>256</v>
+        <v>318</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>257</v>
+        <v>319</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B46" s="16">
         <v>6</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>258</v>
+        <v>320</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>259</v>
+        <v>321</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B47" s="16">
         <v>8</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>260</v>
+        <v>322</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>261</v>
+        <v>323</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B48" s="16">
         <v>9</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>262</v>
+        <v>324</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B49" s="16">
         <v>9</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>264</v>
+        <v>326</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>265</v>
+        <v>327</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B50" s="16">
         <v>8</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>266</v>
+        <v>328</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>267</v>
+        <v>329</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B51" s="16">
         <v>9</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>268</v>
+        <v>330</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>269</v>
+        <v>331</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B52" s="16">
         <v>9</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>270</v>
+        <v>332</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>271</v>
+        <v>333</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B53" s="16">
         <v>9</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>272</v>
+        <v>334</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>273</v>
+        <v>335</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B54" s="16">
         <v>8</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>274</v>
+        <v>336</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>275</v>
+        <v>337</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B55" s="16">
         <v>8</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>276</v>
+        <v>338</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>277</v>
+        <v>339</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B56" s="16">
         <v>8</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>278</v>
+        <v>340</v>
       </c>
       <c r="D56" s="16" t="s">
-        <v>279</v>
+        <v>341</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B57" s="16">
         <v>8</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>280</v>
+        <v>342</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>281</v>
+        <v>343</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="16" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="B58" s="16">
         <v>8</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>282</v>
+        <v>344</v>
       </c>
       <c r="D58" s="16" t="s">
-        <v>283</v>
+        <v>345</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B59" s="16">
         <v>10</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>285</v>
+        <v>347</v>
       </c>
       <c r="D59" s="16" t="s">
-        <v>286</v>
+        <v>348</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B60" s="16">
         <v>12</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>287</v>
+        <v>349</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>288</v>
+        <v>350</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B61" s="16">
         <v>10</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>289</v>
+        <v>351</v>
       </c>
       <c r="D61" s="16" t="s">
-        <v>290</v>
+        <v>352</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B62" s="16">
         <v>11</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>291</v>
+        <v>353</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>292</v>
+        <v>354</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B63" s="16">
         <v>12</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>293</v>
+        <v>355</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>294</v>
+        <v>356</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B64" s="16">
         <v>12</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>295</v>
+        <v>357</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>296</v>
+        <v>358</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B65" s="16">
         <v>12</v>
       </c>
       <c r="C65" s="16" t="s">
-        <v>295</v>
+        <v>357</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>297</v>
+        <v>359</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B66" s="16">
         <v>15</v>
       </c>
       <c r="C66" s="16" t="s">
-        <v>298</v>
+        <v>360</v>
       </c>
       <c r="D66" s="16" t="s">
-        <v>299</v>
+        <v>361</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B67" s="16">
         <v>14</v>
       </c>
       <c r="C67" s="16" t="s">
-        <v>300</v>
+        <v>362</v>
       </c>
       <c r="D67" s="16" t="s">
-        <v>301</v>
+        <v>363</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B68" s="16">
         <v>14</v>
       </c>
       <c r="C68" s="16" t="s">
-        <v>302</v>
+        <v>364</v>
       </c>
       <c r="D68" s="16" t="s">
-        <v>303</v>
+        <v>365</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B69" s="16">
         <v>14</v>
       </c>
       <c r="C69" s="16" t="s">
-        <v>304</v>
+        <v>366</v>
       </c>
       <c r="D69" s="16" t="s">
-        <v>305</v>
+        <v>367</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B70" s="16">
         <v>15</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>306</v>
+        <v>368</v>
       </c>
       <c r="D70" s="16" t="s">
-        <v>307</v>
+        <v>369</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B71" s="16">
         <v>15</v>
       </c>
       <c r="C71" s="16" t="s">
-        <v>308</v>
+        <v>370</v>
       </c>
       <c r="D71" s="16" t="s">
-        <v>309</v>
+        <v>371</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B72" s="16">
         <v>15</v>
       </c>
       <c r="C72" s="16" t="s">
-        <v>310</v>
+        <v>372</v>
       </c>
       <c r="D72" s="16" t="s">
-        <v>311</v>
+        <v>373</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B73" s="16">
         <v>10</v>
       </c>
       <c r="C73" s="16" t="s">
-        <v>312</v>
+        <v>374</v>
       </c>
       <c r="D73" s="16" t="s">
-        <v>313</v>
+        <v>375</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B74" s="16">
         <v>10</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>314</v>
+        <v>376</v>
       </c>
       <c r="D74" s="16" t="s">
-        <v>315</v>
+        <v>377</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B75" s="16">
         <v>8</v>
       </c>
       <c r="C75" s="16" t="s">
-        <v>316</v>
+        <v>378</v>
       </c>
       <c r="D75" s="16" t="s">
-        <v>317</v>
+        <v>379</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B76" s="16">
         <v>10</v>
       </c>
       <c r="C76" s="16" t="s">
-        <v>318</v>
+        <v>380</v>
       </c>
       <c r="D76" s="16" t="s">
-        <v>319</v>
+        <v>381</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B77" s="16">
         <v>7</v>
       </c>
       <c r="C77" s="16" t="s">
-        <v>320</v>
+        <v>382</v>
       </c>
       <c r="D77" s="16" t="s">
-        <v>321</v>
+        <v>383</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B78" s="16">
         <v>8</v>
       </c>
       <c r="C78" s="16" t="s">
-        <v>322</v>
+        <v>384</v>
       </c>
       <c r="D78" s="16" t="s">
-        <v>323</v>
+        <v>385</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B79" s="16">
         <v>5</v>
       </c>
       <c r="C79" s="16" t="s">
-        <v>324</v>
+        <v>386</v>
       </c>
       <c r="D79" s="16" t="s">
-        <v>325</v>
+        <v>387</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B80" s="16">
         <v>6</v>
       </c>
       <c r="C80" s="16" t="s">
-        <v>326</v>
+        <v>388</v>
       </c>
       <c r="D80" s="16" t="s">
-        <v>327</v>
+        <v>389</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B81" s="16">
         <v>6</v>
       </c>
       <c r="C81" s="16" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="D81" s="16" t="s">
-        <v>329</v>
+        <v>391</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B82" s="16">
         <v>6</v>
       </c>
       <c r="C82" s="16" t="s">
-        <v>250</v>
+        <v>312</v>
       </c>
       <c r="D82" s="16" t="s">
-        <v>330</v>
+        <v>392</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B83" s="16">
         <v>6</v>
       </c>
       <c r="C83" s="16" t="s">
-        <v>331</v>
+        <v>393</v>
       </c>
       <c r="D83" s="16" t="s">
-        <v>332</v>
+        <v>394</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B84" s="16">
         <v>5</v>
       </c>
       <c r="C84" s="16" t="s">
-        <v>333</v>
+        <v>395</v>
       </c>
       <c r="D84" s="16" t="s">
-        <v>334</v>
+        <v>396</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B85" s="16">
         <v>7</v>
       </c>
       <c r="C85" s="16" t="s">
-        <v>314</v>
+        <v>376</v>
       </c>
       <c r="D85" s="16" t="s">
-        <v>335</v>
+        <v>397</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B86" s="16">
         <v>8</v>
       </c>
       <c r="C86" s="16" t="s">
-        <v>336</v>
+        <v>398</v>
       </c>
       <c r="D86" s="16" t="s">
-        <v>337</v>
+        <v>399</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B87" s="16">
         <v>8</v>
       </c>
       <c r="C87" s="16" t="s">
-        <v>338</v>
+        <v>400</v>
       </c>
       <c r="D87" s="16" t="s">
-        <v>339</v>
+        <v>401</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B88" s="16">
         <v>8</v>
       </c>
       <c r="C88" s="16" t="s">
-        <v>340</v>
+        <v>402</v>
       </c>
       <c r="D88" s="16" t="s">
-        <v>341</v>
+        <v>403</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B89" s="16">
         <v>8</v>
       </c>
       <c r="C89" s="16" t="s">
-        <v>342</v>
+        <v>404</v>
       </c>
       <c r="D89" s="16" t="s">
-        <v>343</v>
+        <v>405</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B90" s="16">
         <v>8</v>
       </c>
       <c r="C90" s="16" t="s">
-        <v>344</v>
+        <v>406</v>
       </c>
       <c r="D90" s="16" t="s">
-        <v>345</v>
+        <v>407</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="16" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="B91" s="16">
         <v>8</v>
       </c>
       <c r="C91" s="16" t="s">
-        <v>346</v>
+        <v>408</v>
       </c>
       <c r="D91" s="16" t="s">
-        <v>347</v>
+        <v>409</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B92" s="16">
         <v>13</v>
       </c>
       <c r="C92" s="16" t="s">
-        <v>349</v>
+        <v>411</v>
       </c>
       <c r="D92" s="16" t="s">
-        <v>350</v>
+        <v>412</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B93" s="16">
         <v>12</v>
       </c>
       <c r="C93" s="16" t="s">
-        <v>351</v>
+        <v>413</v>
       </c>
       <c r="D93" s="16" t="s">
-        <v>352</v>
+        <v>414</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B94" s="16">
         <v>12</v>
       </c>
       <c r="C94" s="16" t="s">
-        <v>353</v>
+        <v>415</v>
       </c>
       <c r="D94" s="16" t="s">
-        <v>354</v>
+        <v>416</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B95" s="16">
         <v>12</v>
       </c>
       <c r="C95" s="16" t="s">
-        <v>355</v>
+        <v>417</v>
       </c>
       <c r="D95" s="16" t="s">
-        <v>356</v>
+        <v>418</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B96" s="16">
         <v>12</v>
       </c>
       <c r="C96" s="16" t="s">
-        <v>357</v>
+        <v>419</v>
       </c>
       <c r="D96" s="16" t="s">
-        <v>358</v>
+        <v>420</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B97" s="16">
         <v>13</v>
       </c>
       <c r="C97" s="16" t="s">
-        <v>359</v>
+        <v>421</v>
       </c>
       <c r="D97" s="16" t="s">
-        <v>360</v>
+        <v>422</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B98" s="16">
         <v>13</v>
       </c>
       <c r="C98" s="16" t="s">
-        <v>361</v>
+        <v>423</v>
       </c>
       <c r="D98" s="16" t="s">
-        <v>362</v>
+        <v>424</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B99" s="16">
         <v>13</v>
       </c>
       <c r="C99" s="16" t="s">
-        <v>363</v>
+        <v>425</v>
       </c>
       <c r="D99" s="16" t="s">
-        <v>364</v>
+        <v>426</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B100" s="16">
         <v>13</v>
       </c>
       <c r="C100" s="16" t="s">
-        <v>365</v>
+        <v>427</v>
       </c>
       <c r="D100" s="16" t="s">
-        <v>366</v>
+        <v>428</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B101" s="16">
         <v>13</v>
       </c>
       <c r="C101" s="16" t="s">
-        <v>367</v>
+        <v>429</v>
       </c>
       <c r="D101" s="16" t="s">
-        <v>368</v>
+        <v>430</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B102" s="16">
         <v>14</v>
       </c>
       <c r="C102" s="16" t="s">
-        <v>369</v>
+        <v>431</v>
       </c>
       <c r="D102" s="16" t="s">
-        <v>370</v>
+        <v>432</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B103" s="16">
         <v>14</v>
       </c>
       <c r="C103" s="16" t="s">
-        <v>371</v>
+        <v>433</v>
       </c>
       <c r="D103" s="16" t="s">
-        <v>372</v>
+        <v>434</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B104" s="16">
         <v>14</v>
       </c>
       <c r="C104" s="16" t="s">
-        <v>340</v>
+        <v>402</v>
       </c>
       <c r="D104" s="16" t="s">
-        <v>373</v>
+        <v>435</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B105" s="16">
         <v>9</v>
       </c>
       <c r="C105" s="16" t="s">
-        <v>314</v>
+        <v>376</v>
       </c>
       <c r="D105" s="16" t="s">
-        <v>374</v>
+        <v>436</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B106" s="16">
         <v>11</v>
       </c>
       <c r="C106" s="16" t="s">
-        <v>375</v>
+        <v>437</v>
       </c>
       <c r="D106" s="16" t="s">
-        <v>376</v>
+        <v>438</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B107" s="16">
         <v>15</v>
       </c>
       <c r="C107" s="16" t="s">
-        <v>377</v>
+        <v>439</v>
       </c>
       <c r="D107" s="16" t="s">
-        <v>378</v>
+        <v>440</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B108" s="16">
         <v>9</v>
       </c>
       <c r="C108" s="16" t="s">
-        <v>314</v>
+        <v>376</v>
       </c>
       <c r="D108" s="16" t="s">
-        <v>379</v>
+        <v>441</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B109" s="16">
         <v>7</v>
       </c>
       <c r="C109" s="16" t="s">
-        <v>367</v>
+        <v>429</v>
       </c>
       <c r="D109" s="16" t="s">
-        <v>380</v>
+        <v>442</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B110" s="16">
         <v>9</v>
       </c>
       <c r="C110" s="16" t="s">
-        <v>381</v>
+        <v>443</v>
       </c>
       <c r="D110" s="16" t="s">
-        <v>382</v>
+        <v>444</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B111" s="16">
         <v>6</v>
       </c>
       <c r="C111" s="16" t="s">
-        <v>383</v>
+        <v>445</v>
       </c>
       <c r="D111" s="16" t="s">
-        <v>384</v>
+        <v>446</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B112" s="16">
         <v>6</v>
       </c>
       <c r="C112" s="16" t="s">
-        <v>385</v>
+        <v>447</v>
       </c>
       <c r="D112" s="16" t="s">
-        <v>386</v>
+        <v>448</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B113" s="16">
         <v>6</v>
       </c>
       <c r="C113" s="16" t="s">
-        <v>387</v>
+        <v>449</v>
       </c>
       <c r="D113" s="16" t="s">
-        <v>388</v>
+        <v>450</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B114" s="16">
         <v>7</v>
       </c>
       <c r="C114" s="16" t="s">
-        <v>389</v>
+        <v>451</v>
       </c>
       <c r="D114" s="16" t="s">
-        <v>390</v>
+        <v>452</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B115" s="16">
         <v>7</v>
       </c>
       <c r="C115" s="16" t="s">
-        <v>391</v>
+        <v>453</v>
       </c>
       <c r="D115" s="16" t="s">
-        <v>392</v>
+        <v>454</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B116" s="16">
         <v>4</v>
       </c>
       <c r="C116" s="16" t="s">
-        <v>393</v>
+        <v>455</v>
       </c>
       <c r="D116" s="16" t="s">
-        <v>394</v>
+        <v>456</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B117" s="16">
         <v>8</v>
       </c>
       <c r="C117" s="16" t="s">
-        <v>395</v>
+        <v>457</v>
       </c>
       <c r="D117" s="16" t="s">
-        <v>396</v>
+        <v>458</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B118" s="16">
         <v>9</v>
       </c>
       <c r="C118" s="16" t="s">
-        <v>397</v>
+        <v>459</v>
       </c>
       <c r="D118" s="16" t="s">
-        <v>398</v>
+        <v>460</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B119" s="16">
         <v>9</v>
       </c>
       <c r="C119" s="16" t="s">
-        <v>399</v>
+        <v>461</v>
       </c>
       <c r="D119" s="16" t="s">
-        <v>400</v>
+        <v>462</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B120" s="16">
         <v>9</v>
       </c>
       <c r="C120" s="16" t="s">
-        <v>312</v>
+        <v>374</v>
       </c>
       <c r="D120" s="16" t="s">
-        <v>401</v>
+        <v>463</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B121" s="16">
         <v>9</v>
       </c>
       <c r="C121" s="16" t="s">
-        <v>402</v>
+        <v>464</v>
       </c>
       <c r="D121" s="16" t="s">
-        <v>403</v>
+        <v>465</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="16" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="B122" s="16">
         <v>8</v>
       </c>
       <c r="C122" s="16" t="s">
-        <v>404</v>
+        <v>466</v>
       </c>
       <c r="D122" s="16" t="s">
-        <v>405</v>
+        <v>467</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="16" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="B123" s="16">
         <v>17</v>
       </c>
       <c r="C123" s="16" t="s">
-        <v>407</v>
+        <v>469</v>
       </c>
       <c r="D123" s="16" t="s">
-        <v>408</v>
+        <v>470</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="16" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="B124" s="16">
         <v>13</v>
       </c>
       <c r="C124" s="16" t="s">
-        <v>409</v>
+        <v>471</v>
       </c>
       <c r="D124" s="16" t="s">
-        <v>410</v>
+        <v>472</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="16" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="B125" s="16">
         <v>15</v>
       </c>
       <c r="C125" s="16" t="s">
-        <v>411</v>
+        <v>473</v>
       </c>
       <c r="D125" s="16" t="s">
-        <v>412</v>
+        <v>474</v>
       </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="16" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="B126" s="16">
         <v>16</v>
       </c>
       <c r="C126" s="16" t="s">
-        <v>413</v>
+        <v>475</v>
       </c>
       <c r="D126" s="16" t="s">
-        <v>414</v>
+        <v>476</v>
       </c>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="16" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="B127" s="16">
         <v>16</v>
       </c>
       <c r="C127" s="16" t="s">
-        <v>415</v>
+        <v>477</v>
       </c>
       <c r="D127" s="16" t="s">
-        <v>416</v>
+        <v>478</v>
       </c>
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="16" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="B128" s="16">
         <v>17</v>
       </c>
       <c r="C128" s="16" t="s">
-        <v>417</v>
+        <v>479</v>
       </c>
       <c r="D128" s="16" t="s">
-        <v>418</v>
+        <v>480</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="16" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="B129" s="16">
         <v>17</v>
       </c>
       <c r="C129" s="16" t="s">
-        <v>419</v>
+        <v>481</v>
       </c>
       <c r="D129" s="16" t="s">
-        <v>420</v>
+        <v>482</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="16" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="B130" s="16">
         <v>17</v>
       </c>
       <c r="C130" s="16" t="s">
-        <v>421</v>
+        <v>483</v>
       </c>
       <c r="D130" s="16" t="s">
-        <v>422</v>
+        <v>484</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="16" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="B131" s="16">
         <v>17</v>
       </c>
       <c r="C131" s="16" t="s">
-        <v>423</v>
+        <v>485</v>
       </c>
       <c r="D131" s="16" t="s">
-        <v>424</v>
+        <v>486</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="16" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="B132" s="16">
         <v>17</v>
       </c>
       <c r="C132" s="16" t="s">
-        <v>425</v>
+        <v>487</v>
       </c>
       <c r="D132" s="16" t="s">
-        <v>426</v>
+        <v>488</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="16" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="B133" s="16">
         <v>18</v>
       </c>
       <c r="C133" s="16" t="s">
-        <v>427</v>
+        <v>489</v>
       </c>
       <c r="D133" s="16" t="s">
-        <v>428</v>
+        <v>490</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="16" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="B134" s="16">
         <v>19</v>
       </c>
       <c r="C134" s="16" t="s">
-        <v>429</v>
+        <v>491</v>
       </c>
       <c r="D134" s="16" t="s">
-        <v>430</v>
+        <v>492</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="16" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="B135" s="16">
         <v>12</v>
       </c>
       <c r="C135" s="16" t="s">
-        <v>431</v>
+        <v>493</v>
       </c>
       <c r="D135" s="16" t="s">
-        <v>432</v>
+        <v>494</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="16" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="B136" s="16">
         <v>13</v>
       </c>
       <c r="C136" s="16" t="s">
-        <v>433</v>
+        <v>495</v>
       </c>
       <c r="D136" s="16" t="s">
-        <v>434</v>
+        <v>496</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="16" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="B137" s="16">
         <v>12</v>
       </c>
       <c r="C137" s="16" t="s">
-        <v>435</v>
+        <v>497</v>
       </c>
       <c r="D137" s="16" t="s">
-        <v>436</v>
+        <v>498</v>
       </c>
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="16" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="B138" s="16">
         <v>6</v>
       </c>
       <c r="C138" s="16" t="s">
-        <v>437</v>
+        <v>499</v>
       </c>
       <c r="D138" s="16" t="s">
-        <v>438</v>
+        <v>500</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="16" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="B139" s="16">
         <v>9</v>
       </c>
       <c r="C139" s="16" t="s">
-        <v>439</v>
+        <v>501</v>
       </c>
       <c r="D139" s="16" t="s">
-        <v>440</v>
+        <v>502</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="16" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="B140" s="16">
         <v>12</v>
       </c>
       <c r="C140" s="16" t="s">
-        <v>441</v>
+        <v>503</v>
       </c>
       <c r="D140" s="16" t="s">
-        <v>442</v>
+        <v>504</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="16" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="B141" s="16">
         <v>6</v>
       </c>
       <c r="C141" s="16" t="s">
-        <v>443</v>
+        <v>505</v>
       </c>
       <c r="D141" s="16" t="s">
-        <v>444</v>
+        <v>506</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="16" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="B142" s="16">
         <v>6</v>
       </c>
       <c r="C142" s="16" t="s">
-        <v>445</v>
+        <v>507</v>
       </c>
       <c r="D142" s="16" t="s">
-        <v>446</v>
+        <v>508</v>
       </c>
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="16" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="B143" s="16">
         <v>6</v>
       </c>
       <c r="C143" s="16" t="s">
-        <v>447</v>
+        <v>509</v>
       </c>
       <c r="D143" s="16" t="s">
-        <v>448</v>
+        <v>510</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="16" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="B144" s="16">
         <v>3</v>
       </c>
       <c r="C144" s="16" t="s">
-        <v>449</v>
+        <v>511</v>
       </c>
       <c r="D144" s="16" t="s">
-        <v>450</v>
+        <v>512</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="16" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="B145" s="16">
         <v>7</v>
       </c>
       <c r="C145" s="16" t="s">
-        <v>451</v>
+        <v>513</v>
       </c>
       <c r="D145" s="16" t="s">
-        <v>452</v>
+        <v>514</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="16" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="B146" s="16">
         <v>9</v>
       </c>
       <c r="C146" s="16" t="s">
-        <v>453</v>
+        <v>515</v>
       </c>
       <c r="D146" s="16" t="s">
-        <v>454</v>
+        <v>516</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="16" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="B147" s="16">
         <v>9</v>
       </c>
       <c r="C147" s="16" t="s">
-        <v>455</v>
+        <v>517</v>
       </c>
       <c r="D147" s="16" t="s">
-        <v>456</v>
+        <v>518</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="16" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="B148" s="16">
         <v>9</v>
       </c>
       <c r="C148" s="16" t="s">
-        <v>285</v>
+        <v>347</v>
       </c>
       <c r="D148" s="16" t="s">
-        <v>457</v>
+        <v>519</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="16" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="B149" s="16">
         <v>10</v>
       </c>
       <c r="C149" s="16" t="s">
-        <v>458</v>
+        <v>520</v>
       </c>
       <c r="D149" s="16" t="s">
-        <v>459</v>
+        <v>521</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="16" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="B150" s="16">
         <v>10</v>
       </c>
       <c r="C150" s="16" t="s">
-        <v>460</v>
+        <v>522</v>
       </c>
       <c r="D150" s="16" t="s">
-        <v>461</v>
+        <v>523</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="16" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="B151" s="16">
         <v>12</v>
       </c>
       <c r="C151" s="16" t="s">
-        <v>462</v>
+        <v>524</v>
       </c>
       <c r="D151" s="16" t="s">
-        <v>463</v>
+        <v>525</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="16" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="B152" s="16">
         <v>12</v>
       </c>
       <c r="C152" s="16" t="s">
-        <v>464</v>
+        <v>526</v>
       </c>
       <c r="D152" s="16" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="16" t="s">
-        <v>466</v>
+        <v>528</v>
       </c>
       <c r="B153" s="16">
         <v>14</v>
       </c>
       <c r="C153" s="16" t="s">
-        <v>467</v>
+        <v>529</v>
       </c>
       <c r="D153" s="16" t="s">
-        <v>468</v>
+        <v>530</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/NTPC_model.xlsx
+++ b/outputs/NTPC_model.xlsx
@@ -90,7 +90,7 @@
     <t>India 10Y G-sec yield</t>
   </si>
   <si>
-    <t>Trading Economics, 25-Sep-2026</t>
+    <t>Investing.com historical close, 14-Aug-2026</t>
   </si>
   <si>
     <t>Sovereign default spread</t>
@@ -114,7 +114,7 @@
     <t>FY27 fraction remaining</t>
   </si>
   <si>
-    <t>Valuation date 25-Sep-2026</t>
+    <t>Valuation date 14-Aug-2026</t>
   </si>
   <si>
     <t>Weight on 12m DCF in target (non-regulated)</t>
@@ -153,7 +153,7 @@
     <t>Share price (Rs)</t>
   </si>
   <si>
-    <t>NSE close 2026-09-25</t>
+    <t>NSE close 2026-08-14</t>
   </si>
   <si>
     <t>Shares outstanding (crore)</t>
@@ -276,7 +276,7 @@
     <t>NTPC Green market cap</t>
   </si>
   <si>
-    <t>NSE 2026-09-25</t>
+    <t>NSE 2026-08-14</t>
   </si>
   <si>
     <t>NTPC stake in NTPC Green</t>
@@ -681,7 +681,7 @@
     <t>Blue = input, black = formula. Change Inputs or the guided-capex row on Model.</t>
   </si>
   <si>
-    <t>Prices as of 2026-09-25. Student research exercise, not investment advice.</t>
+    <t>Prices as of 2026-08-14. Student research exercise, not investment advice.</t>
   </si>
   <si>
     <t>Listed power comps, FY26A</t>
@@ -2241,7 +2241,7 @@
         <v>4</v>
       </c>
       <c r="C4" s="8">
-        <v>0.0711</v>
+        <v>0.06762</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>5</v>
@@ -2285,7 +2285,7 @@
         <v>12</v>
       </c>
       <c r="C8" s="9">
-        <v>0.51</v>
+        <v>0.6273972602739726</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>13</v>
@@ -2318,7 +2318,7 @@
         <v>18</v>
       </c>
       <c r="C11" s="9">
-        <v>0.797</v>
+        <v>0.879</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>19</v>
@@ -2360,7 +2360,7 @@
         <v>25</v>
       </c>
       <c r="C15" s="10">
-        <v>326.6</v>
+        <v>336.37</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>26</v>
@@ -2404,7 +2404,7 @@
         <v>32</v>
       </c>
       <c r="C19" s="11">
-        <v>14.15362587744053</v>
+        <v>14.60824659966117</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>33</v>
@@ -2647,7 +2647,7 @@
         <v>66</v>
       </c>
       <c r="C44" s="10">
-        <v>78760.90444474769</v>
+        <v>77463.24890426817</v>
       </c>
       <c r="D44" s="7" t="s">
         <v>67</v>
@@ -6683,19 +6683,19 @@
         <v>214</v>
       </c>
       <c r="C4" s="5">
-        <v>390997.185143875</v>
+        <v>395818.358820125</v>
       </c>
       <c r="D4" s="5">
-        <v>444740.665143875</v>
+        <v>449561.838820125</v>
       </c>
       <c r="E4" s="11">
-        <v>22.45484525617868</v>
+        <v>22.69826511259845</v>
       </c>
       <c r="F4" s="11">
-        <v>30.14395074734986</v>
+        <v>30.5156394125453</v>
       </c>
       <c r="G4" s="11">
-        <v>6.021177220134515</v>
+        <v>6.095421082281673</v>
       </c>
       <c r="H4" s="6">
         <v>0.2138946604663434</v>
@@ -6715,19 +6715,19 @@
         <v>215</v>
       </c>
       <c r="C5" s="5">
-        <v>316693.11593644</v>
+        <v>326166.758749358</v>
       </c>
       <c r="D5" s="5">
-        <v>589225.82593644</v>
+        <v>598699.468749358</v>
       </c>
       <c r="E5" s="11">
-        <v>10.62855488900105</v>
+        <v>10.7994420568808</v>
       </c>
       <c r="F5" s="11">
-        <v>11.49688215844188</v>
+        <v>11.84080297500029</v>
       </c>
       <c r="G5" s="11">
-        <v>1.55871321384632</v>
+        <v>1.605340979000266</v>
       </c>
       <c r="H5" s="6">
         <v>0.1422657890183784</v>
@@ -6747,19 +6747,19 @@
         <v>217</v>
       </c>
       <c r="C6" s="5">
-        <v>250651.27292205</v>
+        <v>247442.564604495</v>
       </c>
       <c r="D6" s="5">
-        <v>393788.9629220501</v>
+        <v>390580.254604495</v>
       </c>
       <c r="E6" s="11">
-        <v>11.99442487045932</v>
+        <v>11.89669076800874</v>
       </c>
       <c r="F6" s="11">
-        <v>15.73651889264503</v>
+        <v>15.53506809420486</v>
       </c>
       <c r="G6" s="11">
-        <v>2.494191423587976</v>
+        <v>2.462262071412174</v>
       </c>
       <c r="H6" s="6">
         <v>0.1649228347924227</v>
@@ -6779,19 +6779,19 @@
         <v>219</v>
       </c>
       <c r="C7" s="5">
-        <v>213572.8602573</v>
+        <v>222039.345694</v>
       </c>
       <c r="D7" s="5">
-        <v>322958.8602573</v>
+        <v>331425.345694</v>
       </c>
       <c r="E7" s="11">
-        <v>29.94518871184979</v>
+        <v>30.73021285989801</v>
       </c>
       <c r="F7" s="11">
-        <v>107.4850831692501</v>
+        <v>111.7460219899346</v>
       </c>
       <c r="G7" s="11">
-        <v>10.69736339881292</v>
+        <v>11.12142978682695</v>
       </c>
       <c r="H7" s="6">
         <v>0.1237929100990592</v>
@@ -6811,19 +6811,19 @@
         <v>221</v>
       </c>
       <c r="C8" s="5">
-        <v>117428.72835225</v>
+        <v>122077.947393135</v>
       </c>
       <c r="D8" s="5">
-        <v>195874.79835225</v>
+        <v>200524.017393135</v>
       </c>
       <c r="E8" s="11">
-        <v>14.75961105811544</v>
+        <v>15.10994027527202</v>
       </c>
       <c r="F8" s="11">
-        <v>22.94426110829425</v>
+        <v>23.85266654809203</v>
       </c>
       <c r="G8" s="11">
-        <v>2.975289559953633</v>
+        <v>3.093086738449756</v>
       </c>
       <c r="H8" s="6">
         <v>0.1359200095606103</v>
@@ -6843,19 +6843,19 @@
         <v>223</v>
       </c>
       <c r="C9" s="5">
-        <v>92818.85147831999</v>
+        <v>102612.884864</v>
       </c>
       <c r="D9" s="5">
-        <v>164481.69147832</v>
+        <v>174275.724864</v>
       </c>
       <c r="E9" s="11">
-        <v>16.33707702406834</v>
+        <v>17.30986540166866</v>
       </c>
       <c r="F9" s="11">
-        <v>33.60566671916003</v>
+        <v>37.15165997972484</v>
       </c>
       <c r="G9" s="11">
-        <v>3.018401075682742</v>
+        <v>3.336895868882313</v>
       </c>
       <c r="H9" s="6">
         <v>0.0950578193832599</v>
@@ -6875,19 +6875,19 @@
         <v>225</v>
       </c>
       <c r="C10" s="5">
-        <v>76342.264518</v>
+        <v>77246.31765045</v>
       </c>
       <c r="D10" s="5">
-        <v>132109.384518</v>
+        <v>133013.43765045</v>
       </c>
       <c r="E10" s="11">
-        <v>32.24539529362949</v>
+        <v>32.46605751780572</v>
       </c>
       <c r="F10" s="11">
-        <v>18.09058400900474</v>
+        <v>18.30481460911138</v>
       </c>
       <c r="G10" s="11">
-        <v>1.842369489055675</v>
+        <v>1.864187022478703</v>
       </c>
       <c r="H10" s="6">
         <v>0.1040626348560508</v>
@@ -6907,19 +6907,19 @@
         <v>221</v>
       </c>
       <c r="C11" s="5">
-        <v>63219.73850477999</v>
+        <v>65966.01281412999</v>
       </c>
       <c r="D11" s="5">
-        <v>75504.74850477999</v>
+        <v>78251.02281412999</v>
       </c>
       <c r="E11" s="11">
-        <v>13.53859575126053</v>
+        <v>14.03102435254258</v>
       </c>
       <c r="F11" s="11">
-        <v>25.60540239156743</v>
+        <v>26.71770466347914</v>
       </c>
       <c r="G11" s="11">
-        <v>3.314272005493053</v>
+        <v>3.458244446350196</v>
       </c>
       <c r="H11" s="6">
         <v>0.1345870809484873</v>
@@ -6939,19 +6939,19 @@
         <v>228</v>
       </c>
       <c r="C12" s="5">
-        <v>36406.144169295</v>
+        <v>38151.919660026</v>
       </c>
       <c r="D12" s="5">
-        <v>67334.034169295</v>
+        <v>69079.80966002599</v>
       </c>
       <c r="E12" s="11">
-        <v>12.11479564039133</v>
+        <v>12.42889702411407</v>
       </c>
       <c r="F12" s="11">
-        <v>9.659364332527195</v>
+        <v>10.12255761741205</v>
       </c>
       <c r="G12" s="11">
-        <v>1.691342353974216</v>
+        <v>1.772446906389129</v>
       </c>
       <c r="H12" s="6">
         <v>0.1872888093818326</v>
@@ -6971,19 +6971,19 @@
         <v>225</v>
       </c>
       <c r="C13" s="5">
-        <v>24270.4150008</v>
+        <v>26270.680744875</v>
       </c>
       <c r="D13" s="5">
-        <v>54422.8450008</v>
+        <v>56423.11074487499</v>
       </c>
       <c r="E13" s="11">
-        <v>16.19245611448974</v>
+        <v>16.78759617520827</v>
       </c>
       <c r="F13" s="11">
-        <v>37.8043847364486</v>
+        <v>40.92006346553738</v>
       </c>
       <c r="G13" s="11">
-        <v>1.704502774127397</v>
+        <v>1.844980739158298</v>
       </c>
       <c r="H13" s="6">
         <v>0.045182630727004</v>
@@ -7003,19 +7003,19 @@
         <v>221</v>
       </c>
       <c r="C14" s="5">
-        <v>18539.42803398</v>
+        <v>21453.03183912</v>
       </c>
       <c r="D14" s="5">
-        <v>35265.42803398</v>
+        <v>38179.03183912001</v>
       </c>
       <c r="E14" s="11">
-        <v>9.731078375822296</v>
+        <v>10.53505293573952</v>
       </c>
       <c r="F14" s="11">
-        <v>11.45823735103832</v>
+        <v>13.25898135915946</v>
       </c>
       <c r="G14" s="11">
-        <v>1.47960319505028</v>
+        <v>1.712133426905028</v>
       </c>
       <c r="H14" s="6">
         <v>0.1318663406682966</v>
@@ -7035,19 +7035,19 @@
         <v>214</v>
       </c>
       <c r="C15" s="5">
-        <v>10876.439158449</v>
+        <v>11918.164900153</v>
       </c>
       <c r="D15" s="5">
-        <v>13512.489158449</v>
+        <v>14554.214900153</v>
       </c>
       <c r="E15" s="11">
-        <v>9.884776268068032</v>
+        <v>10.64682874919751</v>
       </c>
       <c r="F15" s="11">
-        <v>24.11627307860089</v>
+        <v>26.42608625311087</v>
       </c>
       <c r="G15" s="11">
-        <v>0.8542600658536758</v>
+        <v>0.9360795554628496</v>
       </c>
       <c r="H15" s="6">
         <v>0.0360612481509615</v>
@@ -7067,16 +7067,16 @@
         <v>214</v>
       </c>
       <c r="C16" s="5">
-        <v>8507.280877061999</v>
+        <v>9504.001679868001</v>
       </c>
       <c r="D16" s="5">
-        <v>22815.030877062</v>
+        <v>23811.751679868</v>
       </c>
       <c r="E16" s="11">
-        <v>9.646947516728121</v>
+        <v>10.0683939449759</v>
       </c>
       <c r="G16" s="11">
-        <v>0.5303791070487531</v>
+        <v>0.5925188079718205</v>
       </c>
       <c r="H16" s="6">
         <v>-0.0208172468110078</v>
@@ -7096,19 +7096,19 @@
         <v>234</v>
       </c>
       <c r="C17" s="5">
-        <v>4590.793050389</v>
+        <v>4779.646359187001</v>
       </c>
       <c r="D17" s="5">
-        <v>2852.353050389</v>
+        <v>3041.206359187</v>
       </c>
       <c r="E17" s="11">
-        <v>3.197705213440583</v>
+        <v>3.409424169492153</v>
       </c>
       <c r="F17" s="11">
-        <v>6.402779707655509</v>
+        <v>6.666173443775454</v>
       </c>
       <c r="G17" s="11">
-        <v>0.7675627905682997</v>
+        <v>0.7991383312467816</v>
       </c>
       <c r="H17" s="6">
         <v>0.1216697777023587</v>
